--- a/list_of_modified_residues/user_list.xlsx
+++ b/list_of_modified_residues/user_list.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="nt" sheetId="1" state="visible" r:id="rId2"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2098" uniqueCount="1516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2095" uniqueCount="1515">
   <si>
     <t xml:space="preserve"># This is a list of modified amino acid residues at N terminal. 
 # Some of the modifications are also present in the side chain and their annottaion is provided in the Comment column 
@@ -402,7 +402,7 @@
     <t xml:space="preserve">Methylation</t>
   </si>
   <si>
-    <t xml:space="preserve">Alanine, Arginine, Aspartic Acid, Asparagine, Cysteine, Glutamine, Glutamic Acid, Glycine, Histidine, Isoleucine, Leucine, Lysine, Methionine, Phenylalanine, Proline, Serine, Threonine, Tryptophan, Tyrosine, Valine</t>
+    <t xml:space="preserve">Alanine, Arginine, Aspartic Acid, Asparagine, Cysteine, Glutamine, Glutamic Acid, Glycine, Histidine, Isoleucine, Leucine, Lysine, Methionine, Proline, Serine, Threonine, Tryptophan, Tyrosine, Valine</t>
   </si>
   <si>
     <t xml:space="preserve">Meth</t>
@@ -731,6 +731,9 @@
     <t xml:space="preserve">Amidation</t>
   </si>
   <si>
+    <t xml:space="preserve">Alanine, Arginine, Aspartic Acid, Asparagine, Cysteine, Glutamine, Glutamic Acid, Glycine, Histidine, Isoleucine, Leucine, Lysine, Methionine, Phenylalanine, Proline, Serine, Threonine, Tryptophan, Tyrosine, Valine</t>
+  </si>
+  <si>
     <t xml:space="preserve">Amid</t>
   </si>
   <si>
@@ -1575,7 +1578,7 @@
     <t xml:space="preserve">One malonic acid group (COCH2COOH) at side chain</t>
   </si>
   <si>
-    <t xml:space="preserve">Alanine, Arginine, Asparagine, Aspartic acid, Cysteine, Glutamine, Histidine, Lysine, Methionine, Serine, Threonine, Tryptophan, Tyrosine</t>
+    <t xml:space="preserve">Alanine, Arginine, Asparagine, Aspartic acid, Cysteine, Glutamine, Histidine, Lysine, Methionine, Phenylalanine, Serine, Threonine, Tryptophan, Tyrosine</t>
   </si>
   <si>
     <t xml:space="preserve">One methyl group at side chain</t>
@@ -1996,7 +1999,7 @@
     <t xml:space="preserve">33W</t>
   </si>
   <si>
-    <t xml:space="preserve">aminobenzoic</t>
+    <t xml:space="preserve">(2S)-2-amino-7,7-dimethyloctanoic acid</t>
   </si>
   <si>
     <t xml:space="preserve">4WQ</t>
@@ -4175,12 +4178,6 @@
   </si>
   <si>
     <t xml:space="preserve">LTU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-TRYPTOPHAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LTR</t>
   </si>
   <si>
     <t xml:space="preserve">(2S)-2-amino-4-(2-aminophenyl)-4-oxobutanoic acid</t>
@@ -4701,7 +4698,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4760,18 +4757,6 @@
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -32803,328 +32788,328 @@
         <v>233</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>125</v>
+        <v>234</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E4" s="7"/>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E5" s="7"/>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>121</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>56</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>125</v>
+        <v>234</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>177</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E15" s="7"/>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>56</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E16" s="7"/>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>64</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E18" s="7"/>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E19" s="7"/>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>64</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E20" s="7"/>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E21" s="7"/>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E22" s="7"/>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>121</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E23" s="7"/>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E24" s="7"/>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E25" s="7"/>
     </row>
@@ -33133,19 +33118,19 @@
         <v>124</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>126</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E26" s="7"/>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>10</v>
@@ -33154,13 +33139,13 @@
         <v>143</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E27" s="7"/>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>114</v>
@@ -33169,37 +33154,37 @@
         <v>139</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E28" s="7"/>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>146</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E29" s="7"/>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>130</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E30" s="7"/>
     </row>
@@ -33214,166 +33199,166 @@
         <v>90</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E31" s="7"/>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E32" s="7"/>
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E33" s="7"/>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>214</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E34" s="7"/>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E35" s="7"/>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>114</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>114</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>114</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>60</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>177</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>97</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -34378,7 +34363,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -34471,13 +34456,13 @@
         <v>5</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
@@ -34504,16 +34489,16 @@
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
@@ -34540,16 +34525,16 @@
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
@@ -34576,16 +34561,16 @@
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
@@ -34618,10 +34603,10 @@
         <v>14</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
@@ -34648,16 +34633,16 @@
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>56</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
@@ -34682,54 +34667,54 @@
       <c r="Y9" s="11"/>
       <c r="Z9" s="11"/>
     </row>
-    <row r="10" s="17" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="15" t="s">
-        <v>369</v>
-      </c>
-      <c r="B10" s="16" t="s">
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
+        <v>370</v>
+      </c>
+      <c r="B10" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="15" t="s">
-        <v>370</v>
-      </c>
-      <c r="D10" s="16" t="s">
+      <c r="C10" s="14" t="s">
         <v>371</v>
       </c>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="16"/>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="16"/>
-      <c r="R10" s="16"/>
-      <c r="S10" s="16"/>
-      <c r="T10" s="16"/>
-      <c r="U10" s="16"/>
-      <c r="V10" s="16"/>
-      <c r="W10" s="16"/>
-      <c r="X10" s="16"/>
-      <c r="Y10" s="16"/>
-      <c r="Z10" s="16"/>
+      <c r="D10" s="11" t="s">
+        <v>372</v>
+      </c>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="11"/>
+      <c r="O10" s="11"/>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="11"/>
+      <c r="R10" s="11"/>
+      <c r="S10" s="11"/>
+      <c r="T10" s="11"/>
+      <c r="U10" s="11"/>
+      <c r="V10" s="11"/>
+      <c r="W10" s="11"/>
+      <c r="X10" s="11"/>
+      <c r="Y10" s="11"/>
+      <c r="Z10" s="11"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
@@ -34756,16 +34741,16 @@
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
@@ -34792,16 +34777,16 @@
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
@@ -34831,13 +34816,13 @@
         <v>36</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C14" s="14" t="s">
         <v>38</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
@@ -34873,7 +34858,7 @@
         <v>42</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
@@ -34900,16 +34885,16 @@
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B16" s="14" t="s">
         <v>56</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E16" s="11"/>
       <c r="F16" s="11"/>
@@ -34936,16 +34921,16 @@
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
@@ -34972,16 +34957,16 @@
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
@@ -35008,16 +34993,16 @@
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B19" s="14" t="s">
         <v>56</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
@@ -35044,16 +35029,16 @@
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E20" s="11"/>
       <c r="F20" s="11"/>
@@ -35080,16 +35065,16 @@
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E21" s="11"/>
       <c r="F21" s="11"/>
@@ -35116,16 +35101,16 @@
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B22" s="14" t="s">
         <v>14</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E22" s="11"/>
       <c r="F22" s="11"/>
@@ -35155,13 +35140,13 @@
         <v>88</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C23" s="14" t="s">
         <v>90</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
@@ -35188,16 +35173,16 @@
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B24" s="14" t="s">
         <v>14</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
@@ -35224,16 +35209,16 @@
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
@@ -35260,16 +35245,16 @@
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="14" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B26" s="14" t="s">
         <v>60</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
@@ -35296,16 +35281,16 @@
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B27" s="14" t="s">
         <v>129</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E27" s="11"/>
       <c r="F27" s="11"/>
@@ -35332,16 +35317,16 @@
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="14" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
@@ -35368,16 +35353,16 @@
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="14" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B29" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E29" s="11"/>
       <c r="F29" s="11"/>
@@ -35404,16 +35389,16 @@
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="14" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B30" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
@@ -35440,16 +35425,16 @@
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="14" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B31" s="14" t="s">
         <v>45</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
@@ -35476,16 +35461,16 @@
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="14" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B32" s="14" t="s">
         <v>45</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
@@ -35512,16 +35497,16 @@
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="14" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B33" s="14" t="s">
         <v>60</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E33" s="11"/>
       <c r="F33" s="11"/>
@@ -35548,16 +35533,16 @@
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="14" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B34" s="14" t="s">
         <v>60</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
@@ -35584,16 +35569,16 @@
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="14" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B35" s="14" t="s">
         <v>60</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
@@ -35620,7 +35605,7 @@
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B36" s="14" t="s">
         <v>45</v>
@@ -35629,7 +35614,7 @@
         <v>94</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
@@ -35656,16 +35641,16 @@
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="14" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B37" s="14" t="s">
         <v>14</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
@@ -35692,16 +35677,16 @@
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="14" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
@@ -35728,16 +35713,16 @@
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B39" s="14" t="s">
         <v>45</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
@@ -35764,16 +35749,16 @@
     </row>
     <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
@@ -35800,16 +35785,16 @@
     </row>
     <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B41" s="14" t="s">
         <v>22</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
@@ -35836,16 +35821,16 @@
     </row>
     <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="14" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
@@ -35872,16 +35857,16 @@
     </row>
     <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="14" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
@@ -35908,16 +35893,16 @@
     </row>
     <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="14" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B44" s="14" t="s">
         <v>60</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
@@ -35944,16 +35929,16 @@
     </row>
     <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="14" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
@@ -35980,16 +35965,16 @@
     </row>
     <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="14" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
@@ -36016,16 +36001,16 @@
     </row>
     <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="14" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B47" s="14" t="s">
         <v>45</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
@@ -36052,16 +36037,16 @@
     </row>
     <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="14" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B48" s="14" t="s">
         <v>45</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
@@ -36088,16 +36073,16 @@
     </row>
     <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="14" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B49" s="14" t="s">
         <v>45</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
@@ -36124,16 +36109,16 @@
     </row>
     <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="14" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B50" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
@@ -36160,16 +36145,16 @@
     </row>
     <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="14" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B51" s="14" t="s">
         <v>129</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
@@ -36196,16 +36181,16 @@
     </row>
     <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="14" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B52" s="14" t="s">
         <v>60</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
@@ -36232,16 +36217,16 @@
     </row>
     <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="14" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B53" s="14" t="s">
         <v>22</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
@@ -36268,16 +36253,16 @@
     </row>
     <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="14" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B54" s="14" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
@@ -36313,7 +36298,7 @@
         <v>115</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
@@ -36343,13 +36328,13 @@
         <v>124</v>
       </c>
       <c r="B56" s="14" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C56" s="14" t="s">
         <v>126</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
@@ -36376,16 +36361,16 @@
     </row>
     <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="14" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B57" s="14" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C57" s="14" t="s">
         <v>143</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
@@ -36412,7 +36397,7 @@
     </row>
     <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="14" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B58" s="14" t="s">
         <v>56</v>
@@ -36421,7 +36406,7 @@
         <v>139</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E58" s="11"/>
       <c r="F58" s="11"/>
@@ -36448,16 +36433,16 @@
     </row>
     <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="14" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B59" s="14" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C59" s="14" t="s">
         <v>146</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E59" s="11"/>
       <c r="F59" s="11"/>
@@ -36484,7 +36469,7 @@
     </row>
     <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="14" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B60" s="14" t="s">
         <v>45</v>
@@ -36493,7 +36478,7 @@
         <v>130</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E60" s="11"/>
       <c r="F60" s="11"/>
@@ -36520,7 +36505,7 @@
     </row>
     <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="14" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B61" s="14" t="s">
         <v>60</v>
@@ -36529,7 +36514,7 @@
         <v>155</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E61" s="11"/>
       <c r="F61" s="11"/>
@@ -36556,16 +36541,16 @@
     </row>
     <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="14" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B62" s="14" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C62" s="14" t="s">
         <v>152</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E62" s="11"/>
       <c r="F62" s="11"/>
@@ -36592,16 +36577,16 @@
     </row>
     <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="14" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B63" s="14" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C63" s="14" t="s">
         <v>136</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E63" s="11"/>
       <c r="F63" s="11"/>
@@ -36628,16 +36613,16 @@
     </row>
     <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="14" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B64" s="14" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C64" s="14" t="s">
         <v>133</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E64" s="11"/>
       <c r="F64" s="11"/>
@@ -36664,7 +36649,7 @@
     </row>
     <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="14" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B65" s="14" t="s">
         <v>114</v>
@@ -36673,7 +36658,7 @@
         <v>161</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E65" s="11"/>
       <c r="F65" s="11"/>
@@ -36700,16 +36685,16 @@
     </row>
     <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="14" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B66" s="14" t="s">
         <v>14</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E66" s="11"/>
       <c r="F66" s="11"/>
@@ -36736,16 +36721,16 @@
     </row>
     <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="14" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B67" s="14" t="s">
         <v>14</v>
       </c>
       <c r="C67" s="14" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E67" s="11"/>
       <c r="F67" s="11"/>
@@ -36772,16 +36757,16 @@
     </row>
     <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="14" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B68" s="14" t="s">
         <v>129</v>
       </c>
       <c r="C68" s="14" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E68" s="11"/>
       <c r="F68" s="11"/>
@@ -36808,16 +36793,16 @@
     </row>
     <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="14" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B69" s="14" t="s">
         <v>22</v>
       </c>
       <c r="C69" s="14" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E69" s="11"/>
       <c r="F69" s="11"/>
@@ -36844,16 +36829,16 @@
     </row>
     <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="14" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B70" s="14" t="s">
         <v>97</v>
       </c>
       <c r="C70" s="14" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E70" s="11"/>
       <c r="F70" s="11"/>
@@ -36880,16 +36865,16 @@
     </row>
     <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="14" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B71" s="14" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C71" s="14" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E71" s="11"/>
       <c r="F71" s="11"/>
@@ -36916,16 +36901,16 @@
     </row>
     <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="14" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B72" s="14" t="s">
         <v>14</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E72" s="11"/>
       <c r="F72" s="11"/>
@@ -36961,7 +36946,7 @@
         <v>196</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E73" s="11"/>
       <c r="F73" s="11"/>
@@ -36988,16 +36973,16 @@
     </row>
     <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="14" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B74" s="14" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C74" s="14" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E74" s="11"/>
       <c r="F74" s="11"/>
@@ -37024,16 +37009,16 @@
     </row>
     <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="14" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B75" s="14" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C75" s="14" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E75" s="11"/>
       <c r="F75" s="11"/>
@@ -37060,16 +37045,16 @@
     </row>
     <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="14" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B76" s="14" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C76" s="14" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E76" s="11"/>
       <c r="F76" s="11"/>
@@ -37096,16 +37081,16 @@
     </row>
     <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="14" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B77" s="14" t="s">
         <v>64</v>
       </c>
       <c r="C77" s="14" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E77" s="11"/>
       <c r="F77" s="11"/>
@@ -37132,16 +37117,16 @@
     </row>
     <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="14" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B78" s="14" t="s">
         <v>64</v>
       </c>
       <c r="C78" s="14" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E78" s="11"/>
       <c r="F78" s="11"/>
@@ -37168,16 +37153,16 @@
     </row>
     <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="14" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B79" s="14" t="s">
         <v>45</v>
       </c>
       <c r="C79" s="14" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E79" s="11"/>
       <c r="F79" s="11"/>
@@ -37204,16 +37189,16 @@
     </row>
     <row r="80" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="14" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B80" s="14" t="s">
         <v>64</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E80" s="11"/>
       <c r="F80" s="11"/>
@@ -37240,7 +37225,7 @@
     </row>
     <row r="81" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="14" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B81" s="14" t="s">
         <v>56</v>
@@ -37249,7 +37234,7 @@
         <v>199</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E81" s="11"/>
       <c r="F81" s="11"/>
@@ -37276,7 +37261,7 @@
     </row>
     <row r="82" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="14" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B82" s="14" t="s">
         <v>56</v>
@@ -37285,7 +37270,7 @@
         <v>203</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E82" s="11"/>
       <c r="F82" s="11"/>
@@ -37312,7 +37297,7 @@
     </row>
     <row r="83" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="14" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B83" s="14" t="s">
         <v>14</v>
@@ -37321,7 +37306,7 @@
         <v>210</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E83" s="11"/>
       <c r="F83" s="11"/>
@@ -37348,16 +37333,16 @@
     </row>
     <row r="84" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="14" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B84" s="14" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C84" s="14" t="s">
         <v>214</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E84" s="11"/>
       <c r="F84" s="11"/>
@@ -37384,16 +37369,16 @@
     </row>
     <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="14" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B85" s="14" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C85" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E85" s="11"/>
       <c r="F85" s="11"/>
@@ -37420,16 +37405,16 @@
     </row>
     <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="14" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B86" s="14" t="s">
         <v>14</v>
       </c>
       <c r="C86" s="14" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E86" s="11"/>
       <c r="F86" s="11"/>
@@ -37456,16 +37441,16 @@
     </row>
     <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="14" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B87" s="14" t="s">
         <v>14</v>
       </c>
       <c r="C87" s="14" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D87" s="11" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E87" s="11"/>
       <c r="F87" s="11"/>
@@ -37492,16 +37477,16 @@
     </row>
     <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="14" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B88" s="14" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C88" s="14" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E88" s="11"/>
       <c r="F88" s="11"/>
@@ -37528,16 +37513,16 @@
     </row>
     <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="14" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B89" s="14" t="s">
         <v>60</v>
       </c>
       <c r="C89" s="14" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D89" s="11" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E89" s="11"/>
       <c r="F89" s="11"/>
@@ -37564,16 +37549,16 @@
     </row>
     <row r="90" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="14" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B90" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C90" s="14" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D90" s="11" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="E90" s="11"/>
       <c r="F90" s="11"/>
@@ -37600,16 +37585,16 @@
     </row>
     <row r="91" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="14" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B91" s="14" t="s">
         <v>45</v>
       </c>
       <c r="C91" s="14" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D91" s="11" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E91" s="11"/>
       <c r="F91" s="11"/>
@@ -37636,16 +37621,16 @@
     </row>
     <row r="92" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="14" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B92" s="14" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C92" s="14" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="E92" s="11"/>
       <c r="F92" s="11"/>
@@ -37672,16 +37657,16 @@
     </row>
     <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="14" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B93" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C93" s="14" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D93" s="11" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E93" s="11"/>
       <c r="F93" s="11"/>
@@ -37708,16 +37693,16 @@
     </row>
     <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="14" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B94" s="14" t="s">
         <v>60</v>
       </c>
       <c r="C94" s="14" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D94" s="11" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E94" s="11"/>
       <c r="F94" s="11"/>
@@ -37744,16 +37729,16 @@
     </row>
     <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="14" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B95" s="14" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C95" s="14" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D95" s="11" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E95" s="11"/>
       <c r="F95" s="11"/>
@@ -37780,16 +37765,16 @@
     </row>
     <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="14" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B96" s="14" t="s">
         <v>45</v>
       </c>
       <c r="C96" s="14" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D96" s="11" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E96" s="11"/>
       <c r="F96" s="11"/>
@@ -37816,16 +37801,16 @@
     </row>
     <row r="97" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="14" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B97" s="14" t="s">
         <v>45</v>
       </c>
       <c r="C97" s="14" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="D97" s="11" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="E97" s="11"/>
       <c r="F97" s="11"/>
@@ -37852,16 +37837,16 @@
     </row>
     <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="14" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B98" s="14" t="s">
         <v>45</v>
       </c>
       <c r="C98" s="14" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D98" s="11" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E98" s="11"/>
       <c r="F98" s="11"/>
@@ -60529,7 +60514,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Z993"/>
+  <dimension ref="A1:Z1048576"/>
   <sheetFormatPr defaultColWidth="12.640625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="64.24"/>
@@ -60541,7 +60526,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -60569,5298 +60554,4726 @@
       <c r="Y1" s="11"/>
       <c r="Z1" s="11"/>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
-        <v>639</v>
-      </c>
-      <c r="B3" s="18" t="s">
+      <c r="A3" s="15" t="s">
+        <v>640</v>
+      </c>
+      <c r="B3" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="15" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="9" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="9" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="9" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="9" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="9" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="9" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="9" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="9" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="9" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="9" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="9" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="9" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="9" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="9" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="9" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="9" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="9" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="9" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="9" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="9" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="9" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="9" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="9" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="9" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="9" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="9" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="9" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="9" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="9" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="9" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="9" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="9" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="9" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="9" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="9" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="9" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="9" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="9" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="9" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="9" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="9" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="9" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="9" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="9" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="9" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="9" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="9" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="9" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="9" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="9" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="9" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="9" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="9" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="9" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="9" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B90" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="9" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B91" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="9" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="9" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="9" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="9" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="9" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="9" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C97" s="9" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="9" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B98" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="9" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B99" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="9" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B100" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="9" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B101" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="9" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B102" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="9" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B103" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="9" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="9" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C105" s="9" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="9" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="9" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C107" s="9" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="9" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B108" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C108" s="9" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="9" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C109" s="9" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="9" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B110" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C110" s="9" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="9" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B111" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C111" s="9" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="9" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B112" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C112" s="9" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="9" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B113" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C113" s="9" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="9" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B114" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C114" s="9" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="9" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B115" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C115" s="9" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="9" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C116" s="9" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="9" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B117" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C117" s="9" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="9" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B118" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C118" s="9" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="9" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C119" s="9" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="9" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B120" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C120" s="9" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="9" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B121" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C121" s="9" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="9" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B122" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C122" s="9" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="9" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B123" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C123" s="9" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="9" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B124" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C124" s="9" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="9" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B125" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C125" s="9" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="9" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B126" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C126" s="9" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="9" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B127" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C127" s="9" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="9" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B128" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C128" s="9" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="9" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B129" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C129" s="9" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="9" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B130" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C130" s="9" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="9" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B131" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C131" s="9" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="9" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B132" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C132" s="9" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="9" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B133" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C133" s="9" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="9" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B134" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C134" s="9" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="9" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B135" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C135" s="9" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="9" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B136" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C136" s="9" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="9" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B137" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C137" s="9" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="9" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B138" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C138" s="9" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="9" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B139" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C139" s="9" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="9" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B140" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C140" s="9" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="9" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B141" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C141" s="9" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="9" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B142" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C142" s="9" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="9" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B143" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C143" s="9" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="9" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B144" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C144" s="9" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="9" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B145" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C145" s="9" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="9" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B146" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C146" s="9" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="9" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B147" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C147" s="9" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="9" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B148" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C148" s="9" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="9" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B149" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C149" s="9" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="9" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B150" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C150" s="9" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="9" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B151" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C151" s="9" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="9" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B152" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C152" s="9" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="9" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B153" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C153" s="9" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="9" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B154" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C154" s="9" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="9" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B155" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C155" s="9" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="9" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B156" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C156" s="9" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="9" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B157" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C157" s="9" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="9" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B158" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C158" s="9" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="9" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B159" s="9" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C159" s="9" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="9" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B160" s="9" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="C160" s="9" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="9" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B161" s="9" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="C161" s="9" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="9" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B162" s="9" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="C162" s="9" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="9" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B163" s="9" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="C163" s="9" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="9" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B164" s="9" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="C164" s="9" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="9" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B165" s="9" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="C165" s="9" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="9" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B166" s="9" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="C166" s="9" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="9" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B167" s="9" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="C167" s="9" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="9" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B168" s="9" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="C168" s="9" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="9" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B169" s="9" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="C169" s="9" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="9" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B170" s="9" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="C170" s="9" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="9" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B171" s="9" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="C171" s="9" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="9" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B172" s="9" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="C172" s="9" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="9" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B173" s="9" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="C173" s="9" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="9" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B174" s="9" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="C174" s="9" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="9" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B175" s="9" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="C175" s="9" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="9" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B176" s="9" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="C176" s="9" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="9" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B177" s="9" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="C177" s="9" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="9" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B178" s="9" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="C178" s="9" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="9" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B179" s="9" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="C179" s="9" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="9" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B180" s="9" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="C180" s="9" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="9" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B181" s="9" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="C181" s="9" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="9" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B182" s="9" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C182" s="9" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="9" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B183" s="9" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C183" s="9" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="9" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B184" s="9" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C184" s="9" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="9" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B185" s="9" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C185" s="9" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="9" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B186" s="9" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C186" s="9" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="9" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B187" s="9" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C187" s="9" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="9" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B188" s="9" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C188" s="9" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="B189" s="9" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C189" s="9" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="9" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="B190" s="9" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C190" s="9" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="9" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="B191" s="9" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C191" s="9" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="9" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B192" s="9" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C192" s="9" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="9" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="B193" s="9" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C193" s="9" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="9" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B194" s="9" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C194" s="9" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="9" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B195" s="9" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C195" s="9" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="9" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B196" s="9" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C196" s="9" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="9" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B197" s="9" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C197" s="9" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="9" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B198" s="9" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="C198" s="9" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="9" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B199" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C199" s="9" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="9" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B200" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C200" s="9" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="9" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B201" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C201" s="9" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="9" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B202" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C202" s="9" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="9" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B203" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C203" s="9" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="9" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B204" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C204" s="9" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="9" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B205" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C205" s="9" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="9" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="B206" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C206" s="9" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="9" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B207" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C207" s="9" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="9" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B208" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C208" s="9" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="9" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B209" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C209" s="9" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="9" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B210" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C210" s="9" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="9" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B211" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C211" s="9" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="9" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B212" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C212" s="9" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="9" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B213" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C213" s="9" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="9" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B214" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C214" s="9" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="9" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B215" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C215" s="9" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="9" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B216" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C216" s="9" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="9" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="B217" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C217" s="9" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="9" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="B218" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C218" s="9" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="9" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="B219" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C219" s="9" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="9" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B220" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C220" s="9" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="9" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="B221" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C221" s="9" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="9" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="B222" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C222" s="9" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="9" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B223" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C223" s="9" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="9" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="B224" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C224" s="9" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="9" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="B225" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C225" s="9" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="9" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B226" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C226" s="9" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="9" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B227" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C227" s="9" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="9" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B228" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C228" s="9" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="9" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B229" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C229" s="9" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="9" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B230" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C230" s="9" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="9" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B231" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C231" s="9" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="9" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B232" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C232" s="9" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="9" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B233" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C233" s="9" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="9" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B234" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C234" s="9" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="9" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="B235" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C235" s="9" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="9" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="B236" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C236" s="9" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="9" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B237" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C237" s="9" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="9" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B238" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C238" s="9" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="9" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B239" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C239" s="9" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="9" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="B240" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C240" s="9" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="9" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B241" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C241" s="9" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="9" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="B242" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C242" s="9" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="9" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="B243" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C243" s="9" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="9" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="B244" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C244" s="9" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="9" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B245" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C245" s="9" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="9" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B246" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C246" s="9" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="9" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B247" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C247" s="9" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="9" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B248" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C248" s="9" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="9" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="B249" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C249" s="9" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="9" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="B250" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C250" s="9" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="9" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B251" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C251" s="9" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="9" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="B252" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C252" s="9" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="9" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="B253" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C253" s="9" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="9" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B254" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C254" s="9" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="9" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="B255" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C255" s="9" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="9" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="B256" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C256" s="9" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="9" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="B257" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C257" s="9" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="9" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="B258" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C258" s="9" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="9" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="B259" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C259" s="9" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="9" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="B260" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C260" s="9" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="9" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B261" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C261" s="9" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="9" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="B262" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C262" s="9" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="9" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="B263" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C263" s="9" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="9" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="B264" s="9" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="C264" s="9" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="9" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="B265" s="9" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="C265" s="9" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="9" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B266" s="9" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="C266" s="9" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="9" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="B267" s="9" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="C267" s="9" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="9" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="B268" s="9" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="C268" s="9" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="9" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="B269" s="9" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="C269" s="9" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="9" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="B270" s="9" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C270" s="9" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="9" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="B271" s="9" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C271" s="9" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="9" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B272" s="9" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C272" s="9" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="9" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="B273" s="9" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C273" s="9" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="9" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="B274" s="9" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C274" s="9" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="9" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="B275" s="9" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C275" s="9" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="9" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="B276" s="9" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C276" s="9" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="9" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="B277" s="9" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C277" s="9" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="9" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="B278" s="9" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C278" s="9" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="9" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="B279" s="9" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C279" s="9" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="9" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="B280" s="9" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C280" s="9" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="9" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="B281" s="9" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C281" s="9" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="9" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="B282" s="9" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C282" s="9" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="9" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="B283" s="9" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C283" s="9" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="9" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="B284" s="9" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C284" s="9" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="9" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B285" s="9" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C285" s="9" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="9" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="B286" s="9" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C286" s="9" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="9" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="B287" s="9" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C287" s="9" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="9" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="B288" s="9" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C288" s="9" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="9" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="B289" s="9" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C289" s="9" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="9" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B290" s="9" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C290" s="9" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="9" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="B291" s="9" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C291" s="9" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="9" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B292" s="9" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C292" s="9" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="9" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="B293" s="9" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C293" s="9" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="294" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="9" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="B294" s="9" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C294" s="9" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="9" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="B295" s="9" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C295" s="9" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="9" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="B296" s="9" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C296" s="9" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="9" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="B297" s="9" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C297" s="9" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="9" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="B298" s="9" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C298" s="9" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="9" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="B299" s="9" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C299" s="9" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="9" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="B300" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C300" s="9" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="301" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="9" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="B301" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C301" s="9" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="302" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="9" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="B302" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C302" s="9" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="9" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B303" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C303" s="9" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="9" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B304" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C304" s="9" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="305" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="9" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B305" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C305" s="9" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="9" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B306" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C306" s="9" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="307" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A307" s="9" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="B307" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C307" s="9" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="9" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="B308" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C308" s="9" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="9" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="B309" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C309" s="9" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="9" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="B310" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C310" s="9" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="9" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="B311" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C311" s="9" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="312" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="9" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B312" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C312" s="9" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="313" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="9" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="B313" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C313" s="9" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="314" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="9" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="B314" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C314" s="9" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="9" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B315" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C315" s="9" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="9" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="B316" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C316" s="9" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="9" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="B317" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C317" s="9" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="318" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="9" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="B318" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C318" s="9" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="319" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="9" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B319" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C319" s="9" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="320" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="9" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B320" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C320" s="9" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="321" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="9" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="B321" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C321" s="9" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="322" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="9" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="B322" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C322" s="9" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="9" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="B323" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C323" s="9" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="324" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="9" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="B324" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C324" s="9" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="325" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A325" s="9" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="B325" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C325" s="9" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="326" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="9" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="B326" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C326" s="9" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="327" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A327" s="9" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="B327" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C327" s="9" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="328" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A328" s="9" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="B328" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C328" s="9" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="329" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A329" s="9" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="B329" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C329" s="9" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="330" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="9" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="B330" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C330" s="9" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="9" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="B331" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C331" s="9" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="332" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="9" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="B332" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C332" s="9" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="333" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A333" s="9" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="B333" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C333" s="9" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="334" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="9" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="B334" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C334" s="9" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="335" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="9" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="B335" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C335" s="9" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="336" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="9" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B336" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C336" s="9" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="337" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="9" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="B337" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C337" s="9" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="338" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A338" s="9" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B338" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C338" s="9" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A339" s="9" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="B339" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C339" s="9" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A340" s="9" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="B340" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C340" s="9" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A341" s="9" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B341" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C341" s="9" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A342" s="9" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="B342" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C342" s="9" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="9" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="B343" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C343" s="9" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="344" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="9" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="B344" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C344" s="9" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="345" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="9" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="B345" s="9" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C345" s="9" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="346" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A346" s="9" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="B346" s="9" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="C346" s="9" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="347" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="9" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="B347" s="9" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="C347" s="9" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="348" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="9" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B348" s="9" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="C348" s="9" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A349" s="9" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="B349" s="9" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="C349" s="9" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="350" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="9" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="B350" s="9" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="C350" s="9" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="9" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="B351" s="9" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="C351" s="9" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="9" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="B352" s="9" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="C352" s="9" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="353" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="9" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B353" s="9" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="C353" s="9" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="354" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="9" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="B354" s="9" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="C354" s="9" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="9" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="B355" s="9" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="C355" s="9" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="356" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="9" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="B356" s="9" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="C356" s="9" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="357" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="9" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="B357" s="9" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="C357" s="9" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="9" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="B358" s="9" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="C358" s="9" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="359" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="9" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="B359" s="9" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="C359" s="9" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A360" s="9" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="B360" s="9" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="C360" s="9" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A361" s="9" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="B361" s="9" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="C361" s="9" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="362" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="9" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="B362" s="9" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="C362" s="9" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="9" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="B363" s="9" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="C363" s="9" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="364" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A364" s="9" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="B364" s="9" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="C364" s="9" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A365" s="9" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="B365" s="9" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="C365" s="9" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="366" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="9" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="B366" s="9" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="C366" s="9" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="367" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="9" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="B367" s="9" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="C367" s="9" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="368" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A368" s="9" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="B368" s="9" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="C368" s="9" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="369" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A369" s="9" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="B369" s="9" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="C369" s="9" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="370" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A370" s="9" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="B370" s="9" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="C370" s="9" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="371" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A371" s="9" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="B371" s="9" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="C371" s="9" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="372" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="9" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="B372" s="9" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="C372" s="9" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="373" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="9" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="B373" s="9" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="C373" s="9" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="374" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A374" s="9" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="B374" s="9" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="C374" s="9" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="375" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A375" s="9" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="B375" s="9" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="C375" s="9" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="376" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="9" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="B376" s="9" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="C376" s="9" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="377" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A377" s="9" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="B377" s="9" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="C377" s="9" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="378" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="9" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="B378" s="9" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="C378" s="9" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="379" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="9" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="B379" s="9" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="C379" s="9" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="380" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="9" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="B380" s="9" t="s">
-        <v>1358</v>
+        <v>1410</v>
       </c>
       <c r="C380" s="9" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="381" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A381" s="9" t="s">
+        <v>1412</v>
+      </c>
+      <c r="B381" s="9" t="s">
         <v>1410</v>
       </c>
-      <c r="B381" s="9" t="s">
-        <v>1411</v>
-      </c>
       <c r="C381" s="9" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="382" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A382" s="9" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="B382" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C382" s="9" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="383" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A383" s="9" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="B383" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C383" s="9" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="384" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A384" s="9" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="B384" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C384" s="9" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="385" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A385" s="9" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="B385" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C385" s="9" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="386" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A386" s="9" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="B386" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C386" s="9" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="387" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A387" s="9" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="B387" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C387" s="9" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="388" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A388" s="9" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="B388" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C388" s="9" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="389" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A389" s="9" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="B389" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C389" s="9" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="390" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A390" s="9" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="B390" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C390" s="9" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="391" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A391" s="9" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="B391" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C391" s="9" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="392" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A392" s="9" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="B392" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C392" s="9" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="393" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A393" s="9" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="B393" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C393" s="9" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="394" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A394" s="9" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="B394" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C394" s="9" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="395" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A395" s="9" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="B395" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C395" s="9" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="396" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A396" s="9" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="B396" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C396" s="9" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="397" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A397" s="9" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="B397" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C397" s="9" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="398" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A398" s="9" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="B398" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C398" s="9" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="399" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A399" s="9" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="B399" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C399" s="9" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="400" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="9" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="B400" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C400" s="9" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="401" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="9" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="B401" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C401" s="9" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="402" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="9" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="B402" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C402" s="9" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="403" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A403" s="9" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="B403" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C403" s="9" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="404" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A404" s="9" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="B404" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C404" s="9" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="405" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A405" s="9" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="B405" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C405" s="9" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="406" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A406" s="9" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="B406" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C406" s="9" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="407" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A407" s="9" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="B407" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C407" s="9" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="408" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A408" s="9" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="B408" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C408" s="9" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="409" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A409" s="9" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="B409" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C409" s="9" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="410" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A410" s="9" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="B410" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C410" s="9" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="411" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="9" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="B411" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C411" s="9" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="412" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A412" s="9" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="B412" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C412" s="9" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="413" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A413" s="9" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="B413" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C413" s="9" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="414" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A414" s="9" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="B414" s="9" t="s">
-        <v>1411</v>
+        <v>1479</v>
       </c>
       <c r="C414" s="9" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="415" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A415" s="9" t="s">
+        <v>1481</v>
+      </c>
+      <c r="B415" s="9" t="s">
         <v>1479</v>
       </c>
-      <c r="B415" s="9" t="s">
-        <v>1480</v>
-      </c>
       <c r="C415" s="9" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="416" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A416" s="9" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="B416" s="9" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="C416" s="9" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="417" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A417" s="9" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="B417" s="9" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="C417" s="9" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="418" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A418" s="9" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="B418" s="9" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="C418" s="9" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="419" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A419" s="9" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="B419" s="9" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="C419" s="9" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="420" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A420" s="9" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="B420" s="9" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="C420" s="9" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="421" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A421" s="9" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="B421" s="9" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="C421" s="9" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="422" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A422" s="9" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="B422" s="9" t="s">
-        <v>1480</v>
+        <v>1410</v>
       </c>
       <c r="C422" s="9" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="423" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="9" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="B423" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C423" s="9" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="424" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A424" s="9" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="B424" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C424" s="9" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="425" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A425" s="9" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="B425" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C425" s="9" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="426" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A426" s="9" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="B426" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C426" s="9" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="427" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A427" s="9" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="B427" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C427" s="9" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="428" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A428" s="9" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="B428" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C428" s="9" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="429" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="9" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="B429" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C429" s="9" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="430" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="9" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="B430" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C430" s="9" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="431" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A431" s="9" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="B431" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C431" s="9" t="s">
-        <v>1513</v>
-      </c>
-    </row>
-    <row r="432" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A432" s="9" t="s">
         <v>1514</v>
       </c>
-      <c r="B432" s="9" t="s">
-        <v>1411</v>
-      </c>
-      <c r="C432" s="9" t="s">
-        <v>1515</v>
-      </c>
-    </row>
-    <row r="433" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="434" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="435" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="436" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="437" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="438" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="439" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="440" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="441" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="442" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="443" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="444" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="445" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="446" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="447" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="448" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="449" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="450" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="451" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="452" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="453" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="454" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="455" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="456" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="457" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="458" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="459" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="460" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="461" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="462" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="463" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="464" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="465" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="466" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="467" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="468" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="469" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="470" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="471" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="472" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="473" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="474" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="475" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="476" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="477" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="478" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="479" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="480" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="481" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="482" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="483" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="484" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="485" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="486" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="487" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="488" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="489" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="490" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="491" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="492" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="493" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="494" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="495" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="496" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="497" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="498" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="499" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="500" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="501" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="502" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="503" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="504" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="505" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="506" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="507" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="508" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="509" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="510" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="511" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="512" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="513" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="514" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="515" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="516" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="517" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="518" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="519" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="520" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="521" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="522" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="523" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="524" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="525" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="526" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="527" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="528" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="529" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="530" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="531" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="532" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="533" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="534" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="535" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="536" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="537" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="538" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="539" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="540" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="541" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="542" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="543" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="544" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="545" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="546" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="547" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="548" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="549" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="550" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="551" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="552" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="553" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="554" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="555" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="556" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="557" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="558" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="559" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="560" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="561" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="562" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="563" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="564" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="565" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="566" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="567" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="568" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="569" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="570" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="571" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="572" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="573" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="574" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="575" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="576" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="577" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="578" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="579" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="580" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="581" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="582" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="583" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="584" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="585" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="586" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="587" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="588" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="589" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="590" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="591" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="592" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="593" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="594" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="595" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="596" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="597" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="598" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="599" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="600" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="601" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="602" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="603" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="604" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="605" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="606" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="607" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="608" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="609" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="610" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="611" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="612" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="613" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="614" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="615" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="616" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="617" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="618" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="619" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="620" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="621" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="622" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="623" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="624" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="625" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="626" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="627" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="628" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="629" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="630" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="631" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="632" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="633" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="634" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="635" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="636" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="637" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="638" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="639" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="640" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="641" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="642" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="643" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="644" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="645" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="646" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="647" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="648" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="649" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="650" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="651" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="652" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="653" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="654" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="655" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="656" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="657" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="658" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="659" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="660" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="661" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="662" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="663" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="664" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="665" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="666" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="667" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="668" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="669" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="670" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="671" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="672" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="673" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="674" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="675" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="676" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="677" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="678" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="679" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="680" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="681" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="682" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="683" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="684" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="685" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="686" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="687" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="688" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="689" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="690" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="691" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="692" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="693" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="694" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="695" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="696" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="697" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="698" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="699" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="700" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="701" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="702" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="703" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="704" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="705" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="706" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="707" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="708" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="709" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="710" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="711" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="712" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="713" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="714" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="715" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="716" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="717" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="718" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="719" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="720" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="721" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="722" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="723" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="724" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="725" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="726" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="727" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="728" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="729" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="730" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="731" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="732" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="733" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="734" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="735" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="736" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="737" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="738" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="739" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="740" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="741" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="742" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="743" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="744" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="745" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="746" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="747" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="748" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="749" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="750" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="751" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="752" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="753" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="754" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="755" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="756" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="757" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="758" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="759" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="760" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="761" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="762" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="763" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="764" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="765" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="766" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="767" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="768" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="769" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="770" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="771" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="772" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="773" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="774" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="775" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="776" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="777" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="778" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="779" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="780" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="781" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="782" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="783" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="784" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="785" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="786" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="787" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="788" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="789" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="790" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="791" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="792" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="793" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="794" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="795" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="796" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="797" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="798" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="799" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="800" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="801" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="802" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="803" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="804" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="805" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="806" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="807" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="808" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="809" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="810" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="811" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="812" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="813" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="814" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="815" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="816" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="817" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="818" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="819" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="820" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="821" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="822" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="823" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="824" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="825" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="826" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="827" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="828" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="829" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="830" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="831" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="832" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="833" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="834" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="835" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="836" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="837" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="838" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="839" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="840" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="841" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="842" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="843" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="844" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="845" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="846" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="847" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="848" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="849" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="850" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="851" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="852" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="853" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="854" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="855" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="856" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="857" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="858" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="859" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="860" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="861" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="862" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="863" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="864" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="865" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="866" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="867" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="868" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="869" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="870" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="871" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="872" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="873" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="874" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="875" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="876" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="877" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="878" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="879" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="880" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="881" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="882" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="883" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="884" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="885" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="886" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="887" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="888" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="889" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="890" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="891" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="892" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="893" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="894" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="895" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="896" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="897" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="898" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="899" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="900" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="901" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="902" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="903" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="904" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="905" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="906" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="907" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="908" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="909" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="910" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="911" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="912" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="913" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="914" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="915" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="916" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="917" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="918" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="919" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="920" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="921" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="922" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="923" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="924" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="925" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="926" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="927" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="928" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="929" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="930" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="931" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="932" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="933" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="934" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="935" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="936" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="937" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="938" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="939" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="940" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="941" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="942" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="943" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="944" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="945" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="946" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="947" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="948" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="949" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="950" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="951" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="952" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="953" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="954" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="955" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="956" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="957" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="958" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="959" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="960" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="961" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="962" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="963" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="964" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="965" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="966" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="967" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="968" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="969" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="970" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="971" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="972" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="973" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="974" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="975" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="976" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="977" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="978" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="979" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="980" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="981" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="982" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="983" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="984" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="985" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="986" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="987" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="988" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="989" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="990" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="991" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="992" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="993" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>

--- a/list_of_modified_residues/user_list.xlsx
+++ b/list_of_modified_residues/user_list.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2095" uniqueCount="1515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2099" uniqueCount="1518">
   <si>
     <t xml:space="preserve"># This is a list of modified amino acid residues at N terminal. 
 # Some of the modifications are also present in the side chain and their annottaion is provided in the Comment column 
@@ -1246,6 +1246,15 @@
   </si>
   <si>
     <t xml:space="preserve">One cyano (CN) group at side chain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deamination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deamino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha-amino removed</t>
   </si>
   <si>
     <t xml:space="preserve">Dehydrogenation</t>
@@ -34350,7 +34359,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Z906"/>
+  <dimension ref="A1:Z907"/>
   <sheetFormatPr defaultColWidth="12.640625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="20.88"/>
@@ -35068,13 +35077,13 @@
         <v>406</v>
       </c>
       <c r="B21" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="14" t="s">
         <v>407</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="D21" s="11" t="s">
         <v>408</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>409</v>
       </c>
       <c r="E21" s="11"/>
       <c r="F21" s="11"/>
@@ -35101,10 +35110,10 @@
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
+        <v>409</v>
+      </c>
+      <c r="B22" s="14" t="s">
         <v>410</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>14</v>
       </c>
       <c r="C22" s="14" t="s">
         <v>411</v>
@@ -35137,16 +35146,16 @@
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>88</v>
+        <v>413</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>413</v>
+        <v>14</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>90</v>
+        <v>414</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
@@ -35173,13 +35182,13 @@
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="s">
-        <v>415</v>
+        <v>88</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>14</v>
+        <v>416</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>416</v>
+        <v>90</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>417</v>
@@ -35212,13 +35221,13 @@
         <v>418</v>
       </c>
       <c r="B25" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="14" t="s">
         <v>419</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="D25" s="11" t="s">
         <v>420</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>421</v>
       </c>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
@@ -35245,10 +35254,10 @@
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="14" t="s">
+        <v>421</v>
+      </c>
+      <c r="B26" s="14" t="s">
         <v>422</v>
-      </c>
-      <c r="B26" s="14" t="s">
-        <v>60</v>
       </c>
       <c r="C26" s="14" t="s">
         <v>423</v>
@@ -35284,7 +35293,7 @@
         <v>425</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>129</v>
+        <v>60</v>
       </c>
       <c r="C27" s="14" t="s">
         <v>426</v>
@@ -35320,13 +35329,13 @@
         <v>428</v>
       </c>
       <c r="B28" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="C28" s="14" t="s">
         <v>429</v>
       </c>
-      <c r="C28" s="14" t="s">
+      <c r="D28" s="11" t="s">
         <v>430</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>431</v>
       </c>
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
@@ -35353,10 +35362,10 @@
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="14" t="s">
+        <v>431</v>
+      </c>
+      <c r="B29" s="14" t="s">
         <v>432</v>
-      </c>
-      <c r="B29" s="14" t="s">
-        <v>10</v>
       </c>
       <c r="C29" s="14" t="s">
         <v>433</v>
@@ -35428,7 +35437,7 @@
         <v>438</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="C31" s="14" t="s">
         <v>439</v>
@@ -35500,7 +35509,7 @@
         <v>444</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="C33" s="14" t="s">
         <v>445</v>
@@ -35608,13 +35617,13 @@
         <v>453</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>94</v>
+        <v>454</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
@@ -35641,13 +35650,13 @@
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="14" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>456</v>
+        <v>94</v>
       </c>
       <c r="D37" s="11" t="s">
         <v>457</v>
@@ -35680,13 +35689,13 @@
         <v>458</v>
       </c>
       <c r="B38" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38" s="14" t="s">
         <v>459</v>
       </c>
-      <c r="C38" s="14" t="s">
+      <c r="D38" s="11" t="s">
         <v>460</v>
-      </c>
-      <c r="D38" s="11" t="s">
-        <v>461</v>
       </c>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
@@ -35713,10 +35722,10 @@
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="B39" s="14" t="s">
         <v>462</v>
-      </c>
-      <c r="B39" s="14" t="s">
-        <v>45</v>
       </c>
       <c r="C39" s="14" t="s">
         <v>463</v>
@@ -35752,13 +35761,13 @@
         <v>465</v>
       </c>
       <c r="B40" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C40" s="14" t="s">
         <v>466</v>
       </c>
-      <c r="C40" s="14" t="s">
+      <c r="D40" s="11" t="s">
         <v>467</v>
-      </c>
-      <c r="D40" s="11" t="s">
-        <v>468</v>
       </c>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
@@ -35785,10 +35794,10 @@
     </row>
     <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
+        <v>468</v>
+      </c>
+      <c r="B41" s="14" t="s">
         <v>469</v>
-      </c>
-      <c r="B41" s="14" t="s">
-        <v>22</v>
       </c>
       <c r="C41" s="14" t="s">
         <v>470</v>
@@ -35824,13 +35833,13 @@
         <v>472</v>
       </c>
       <c r="B42" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C42" s="14" t="s">
         <v>473</v>
       </c>
-      <c r="C42" s="14" t="s">
+      <c r="D42" s="11" t="s">
         <v>474</v>
-      </c>
-      <c r="D42" s="11" t="s">
-        <v>475</v>
       </c>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
@@ -35857,16 +35866,16 @@
     </row>
     <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="14" t="s">
+        <v>475</v>
+      </c>
+      <c r="B43" s="14" t="s">
         <v>476</v>
       </c>
-      <c r="B43" s="14" t="s">
+      <c r="C43" s="14" t="s">
         <v>477</v>
       </c>
-      <c r="C43" s="14" t="s">
+      <c r="D43" s="11" t="s">
         <v>478</v>
-      </c>
-      <c r="D43" s="11" t="s">
-        <v>479</v>
       </c>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
@@ -35893,10 +35902,10 @@
     </row>
     <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="14" t="s">
+        <v>479</v>
+      </c>
+      <c r="B44" s="14" t="s">
         <v>480</v>
-      </c>
-      <c r="B44" s="14" t="s">
-        <v>60</v>
       </c>
       <c r="C44" s="14" t="s">
         <v>481</v>
@@ -35932,13 +35941,13 @@
         <v>483</v>
       </c>
       <c r="B45" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C45" s="14" t="s">
         <v>484</v>
       </c>
-      <c r="C45" s="14" t="s">
+      <c r="D45" s="11" t="s">
         <v>485</v>
-      </c>
-      <c r="D45" s="11" t="s">
-        <v>486</v>
       </c>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
@@ -35965,10 +35974,10 @@
     </row>
     <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="14" t="s">
+        <v>486</v>
+      </c>
+      <c r="B46" s="14" t="s">
         <v>487</v>
-      </c>
-      <c r="B46" s="14" t="s">
-        <v>323</v>
       </c>
       <c r="C46" s="14" t="s">
         <v>488</v>
@@ -36004,7 +36013,7 @@
         <v>490</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>45</v>
+        <v>323</v>
       </c>
       <c r="C47" s="14" t="s">
         <v>491</v>
@@ -36112,7 +36121,7 @@
         <v>499</v>
       </c>
       <c r="B50" s="14" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C50" s="14" t="s">
         <v>500</v>
@@ -36148,7 +36157,7 @@
         <v>502</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>129</v>
+        <v>10</v>
       </c>
       <c r="C51" s="14" t="s">
         <v>503</v>
@@ -36184,7 +36193,7 @@
         <v>505</v>
       </c>
       <c r="B52" s="14" t="s">
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="C52" s="14" t="s">
         <v>506</v>
@@ -36220,7 +36229,7 @@
         <v>508</v>
       </c>
       <c r="B53" s="14" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="C53" s="14" t="s">
         <v>509</v>
@@ -36256,13 +36265,13 @@
         <v>511</v>
       </c>
       <c r="B54" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C54" s="14" t="s">
         <v>512</v>
       </c>
-      <c r="C54" s="14" t="s">
+      <c r="D54" s="11" t="s">
         <v>513</v>
-      </c>
-      <c r="D54" s="11" t="s">
-        <v>514</v>
       </c>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
@@ -36289,16 +36298,16 @@
     </row>
     <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="14" t="s">
-        <v>113</v>
+        <v>514</v>
       </c>
       <c r="B55" s="14" t="s">
-        <v>14</v>
+        <v>515</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="D55" s="14" t="s">
-        <v>515</v>
+        <v>516</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>517</v>
       </c>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
@@ -36325,16 +36334,16 @@
     </row>
     <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="14" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="B56" s="14" t="s">
-        <v>516</v>
+        <v>14</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="D56" s="11" t="s">
-        <v>517</v>
+        <v>115</v>
+      </c>
+      <c r="D56" s="14" t="s">
+        <v>518</v>
       </c>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
@@ -36361,13 +36370,13 @@
     </row>
     <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="14" t="s">
-        <v>518</v>
+        <v>124</v>
       </c>
       <c r="B57" s="14" t="s">
         <v>519</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="D57" s="11" t="s">
         <v>520</v>
@@ -36400,13 +36409,13 @@
         <v>521</v>
       </c>
       <c r="B58" s="14" t="s">
-        <v>56</v>
+        <v>522</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E58" s="11"/>
       <c r="F58" s="11"/>
@@ -36433,13 +36442,13 @@
     </row>
     <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="14" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B59" s="14" t="s">
-        <v>524</v>
+        <v>56</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="D59" s="11" t="s">
         <v>525</v>
@@ -36472,13 +36481,13 @@
         <v>526</v>
       </c>
       <c r="B60" s="14" t="s">
-        <v>45</v>
+        <v>527</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E60" s="11"/>
       <c r="F60" s="11"/>
@@ -36505,16 +36514,16 @@
     </row>
     <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="14" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B61" s="14" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E61" s="11"/>
       <c r="F61" s="11"/>
@@ -36541,13 +36550,13 @@
     </row>
     <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="14" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B62" s="14" t="s">
-        <v>531</v>
+        <v>60</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D62" s="11" t="s">
         <v>532</v>
@@ -36580,13 +36589,13 @@
         <v>533</v>
       </c>
       <c r="B63" s="14" t="s">
-        <v>338</v>
+        <v>534</v>
       </c>
       <c r="C63" s="14" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E63" s="11"/>
       <c r="F63" s="11"/>
@@ -36613,13 +36622,13 @@
     </row>
     <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="14" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B64" s="14" t="s">
-        <v>536</v>
+        <v>338</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D64" s="11" t="s">
         <v>537</v>
@@ -36652,13 +36661,13 @@
         <v>538</v>
       </c>
       <c r="B65" s="14" t="s">
-        <v>114</v>
+        <v>539</v>
       </c>
       <c r="C65" s="14" t="s">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E65" s="11"/>
       <c r="F65" s="11"/>
@@ -36685,13 +36694,13 @@
     </row>
     <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="14" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B66" s="14" t="s">
-        <v>14</v>
+        <v>114</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>541</v>
+        <v>161</v>
       </c>
       <c r="D66" s="11" t="s">
         <v>542</v>
@@ -36760,7 +36769,7 @@
         <v>546</v>
       </c>
       <c r="B68" s="14" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="C68" s="14" t="s">
         <v>547</v>
@@ -36796,7 +36805,7 @@
         <v>549</v>
       </c>
       <c r="B69" s="14" t="s">
-        <v>22</v>
+        <v>129</v>
       </c>
       <c r="C69" s="14" t="s">
         <v>550</v>
@@ -36832,7 +36841,7 @@
         <v>552</v>
       </c>
       <c r="B70" s="14" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="C70" s="14" t="s">
         <v>553</v>
@@ -36868,13 +36877,13 @@
         <v>555</v>
       </c>
       <c r="B71" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="C71" s="14" t="s">
         <v>556</v>
       </c>
-      <c r="C71" s="14" t="s">
+      <c r="D71" s="11" t="s">
         <v>557</v>
-      </c>
-      <c r="D71" s="11" t="s">
-        <v>558</v>
       </c>
       <c r="E71" s="11"/>
       <c r="F71" s="11"/>
@@ -36901,10 +36910,10 @@
     </row>
     <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="14" t="s">
+        <v>558</v>
+      </c>
+      <c r="B72" s="14" t="s">
         <v>559</v>
-      </c>
-      <c r="B72" s="14" t="s">
-        <v>14</v>
       </c>
       <c r="C72" s="14" t="s">
         <v>560</v>
@@ -36937,16 +36946,16 @@
     </row>
     <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="14" t="s">
-        <v>194</v>
+        <v>562</v>
       </c>
       <c r="B73" s="14" t="s">
         <v>14</v>
       </c>
       <c r="C73" s="14" t="s">
-        <v>196</v>
+        <v>563</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="E73" s="11"/>
       <c r="F73" s="11"/>
@@ -36973,16 +36982,16 @@
     </row>
     <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="14" t="s">
-        <v>563</v>
+        <v>194</v>
       </c>
       <c r="B74" s="14" t="s">
-        <v>564</v>
+        <v>14</v>
       </c>
       <c r="C74" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="D74" s="11" t="s">
         <v>565</v>
-      </c>
-      <c r="D74" s="11" t="s">
-        <v>566</v>
       </c>
       <c r="E74" s="11"/>
       <c r="F74" s="11"/>
@@ -37009,16 +37018,16 @@
     </row>
     <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="14" t="s">
+        <v>566</v>
+      </c>
+      <c r="B75" s="14" t="s">
         <v>567</v>
       </c>
-      <c r="B75" s="14" t="s">
+      <c r="C75" s="14" t="s">
         <v>568</v>
       </c>
-      <c r="C75" s="14" t="s">
+      <c r="D75" s="11" t="s">
         <v>569</v>
-      </c>
-      <c r="D75" s="11" t="s">
-        <v>570</v>
       </c>
       <c r="E75" s="11"/>
       <c r="F75" s="11"/>
@@ -37045,10 +37054,10 @@
     </row>
     <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="14" t="s">
+        <v>570</v>
+      </c>
+      <c r="B76" s="14" t="s">
         <v>571</v>
-      </c>
-      <c r="B76" s="14" t="s">
-        <v>536</v>
       </c>
       <c r="C76" s="14" t="s">
         <v>572</v>
@@ -37084,7 +37093,7 @@
         <v>574</v>
       </c>
       <c r="B77" s="14" t="s">
-        <v>64</v>
+        <v>539</v>
       </c>
       <c r="C77" s="14" t="s">
         <v>575</v>
@@ -37156,7 +37165,7 @@
         <v>580</v>
       </c>
       <c r="B79" s="14" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="C79" s="14" t="s">
         <v>581</v>
@@ -37192,7 +37201,7 @@
         <v>583</v>
       </c>
       <c r="B80" s="14" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="C80" s="14" t="s">
         <v>584</v>
@@ -37228,13 +37237,13 @@
         <v>586</v>
       </c>
       <c r="B81" s="14" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C81" s="14" t="s">
-        <v>199</v>
+        <v>587</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E81" s="11"/>
       <c r="F81" s="11"/>
@@ -37261,16 +37270,16 @@
     </row>
     <row r="82" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="14" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B82" s="14" t="s">
         <v>56</v>
       </c>
       <c r="C82" s="14" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E82" s="11"/>
       <c r="F82" s="11"/>
@@ -37297,16 +37306,16 @@
     </row>
     <row r="83" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="14" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B83" s="14" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="C83" s="14" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E83" s="11"/>
       <c r="F83" s="11"/>
@@ -37333,13 +37342,13 @@
     </row>
     <row r="84" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="14" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B84" s="14" t="s">
-        <v>593</v>
+        <v>14</v>
       </c>
       <c r="C84" s="14" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D84" s="11" t="s">
         <v>594</v>
@@ -37369,16 +37378,16 @@
     </row>
     <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="14" t="s">
-        <v>315</v>
+        <v>595</v>
       </c>
       <c r="B85" s="14" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C85" s="14" t="s">
-        <v>317</v>
+        <v>214</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="E85" s="11"/>
       <c r="F85" s="11"/>
@@ -37405,13 +37414,13 @@
     </row>
     <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="14" t="s">
-        <v>597</v>
+        <v>315</v>
       </c>
       <c r="B86" s="14" t="s">
-        <v>14</v>
+        <v>598</v>
       </c>
       <c r="C86" s="14" t="s">
-        <v>598</v>
+        <v>317</v>
       </c>
       <c r="D86" s="11" t="s">
         <v>599</v>
@@ -37480,13 +37489,13 @@
         <v>603</v>
       </c>
       <c r="B88" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C88" s="14" t="s">
         <v>604</v>
       </c>
-      <c r="C88" s="14" t="s">
+      <c r="D88" s="11" t="s">
         <v>605</v>
-      </c>
-      <c r="D88" s="11" t="s">
-        <v>606</v>
       </c>
       <c r="E88" s="11"/>
       <c r="F88" s="11"/>
@@ -37513,10 +37522,10 @@
     </row>
     <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="14" t="s">
+        <v>606</v>
+      </c>
+      <c r="B89" s="14" t="s">
         <v>607</v>
-      </c>
-      <c r="B89" s="14" t="s">
-        <v>60</v>
       </c>
       <c r="C89" s="14" t="s">
         <v>608</v>
@@ -37552,7 +37561,7 @@
         <v>610</v>
       </c>
       <c r="B90" s="14" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="C90" s="14" t="s">
         <v>611</v>
@@ -37588,7 +37597,7 @@
         <v>613</v>
       </c>
       <c r="B91" s="14" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="C91" s="14" t="s">
         <v>614</v>
@@ -37624,13 +37633,13 @@
         <v>616</v>
       </c>
       <c r="B92" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C92" s="14" t="s">
         <v>617</v>
       </c>
-      <c r="C92" s="14" t="s">
+      <c r="D92" s="11" t="s">
         <v>618</v>
-      </c>
-      <c r="D92" s="11" t="s">
-        <v>619</v>
       </c>
       <c r="E92" s="11"/>
       <c r="F92" s="11"/>
@@ -37657,10 +37666,10 @@
     </row>
     <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="14" t="s">
+        <v>619</v>
+      </c>
+      <c r="B93" s="14" t="s">
         <v>620</v>
-      </c>
-      <c r="B93" s="14" t="s">
-        <v>10</v>
       </c>
       <c r="C93" s="14" t="s">
         <v>621</v>
@@ -37696,7 +37705,7 @@
         <v>623</v>
       </c>
       <c r="B94" s="14" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="C94" s="14" t="s">
         <v>624</v>
@@ -37732,13 +37741,13 @@
         <v>626</v>
       </c>
       <c r="B95" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C95" s="14" t="s">
         <v>627</v>
       </c>
-      <c r="C95" s="14" t="s">
+      <c r="D95" s="11" t="s">
         <v>628</v>
-      </c>
-      <c r="D95" s="11" t="s">
-        <v>629</v>
       </c>
       <c r="E95" s="11"/>
       <c r="F95" s="11"/>
@@ -37765,10 +37774,10 @@
     </row>
     <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="14" t="s">
+        <v>629</v>
+      </c>
+      <c r="B96" s="14" t="s">
         <v>630</v>
-      </c>
-      <c r="B96" s="14" t="s">
-        <v>45</v>
       </c>
       <c r="C96" s="14" t="s">
         <v>631</v>
@@ -37872,10 +37881,18 @@
       <c r="Z98" s="11"/>
     </row>
     <row r="99" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="11"/>
-      <c r="B99" s="11"/>
-      <c r="C99" s="11"/>
-      <c r="D99" s="11"/>
+      <c r="A99" s="14" t="s">
+        <v>639</v>
+      </c>
+      <c r="B99" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C99" s="14" t="s">
+        <v>640</v>
+      </c>
+      <c r="D99" s="11" t="s">
+        <v>641</v>
+      </c>
       <c r="E99" s="11"/>
       <c r="F99" s="11"/>
       <c r="G99" s="11"/>
@@ -60494,6 +60511,34 @@
       <c r="X906" s="11"/>
       <c r="Y906" s="11"/>
       <c r="Z906" s="11"/>
+    </row>
+    <row r="907" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A907" s="11"/>
+      <c r="B907" s="11"/>
+      <c r="C907" s="11"/>
+      <c r="D907" s="11"/>
+      <c r="E907" s="11"/>
+      <c r="F907" s="11"/>
+      <c r="G907" s="11"/>
+      <c r="H907" s="11"/>
+      <c r="I907" s="11"/>
+      <c r="J907" s="11"/>
+      <c r="K907" s="11"/>
+      <c r="L907" s="11"/>
+      <c r="M907" s="11"/>
+      <c r="N907" s="11"/>
+      <c r="O907" s="11"/>
+      <c r="P907" s="11"/>
+      <c r="Q907" s="11"/>
+      <c r="R907" s="11"/>
+      <c r="S907" s="11"/>
+      <c r="T907" s="11"/>
+      <c r="U907" s="11"/>
+      <c r="V907" s="11"/>
+      <c r="W907" s="11"/>
+      <c r="X907" s="11"/>
+      <c r="Y907" s="11"/>
+      <c r="Z907" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -60526,7 +60571,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -60556,7 +60601,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>2</v>
@@ -60567,4710 +60612,4710 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="9" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="9" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="9" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="9" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="9" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="9" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="9" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="9" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="9" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="9" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="9" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="9" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="9" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="9" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="9" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="9" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="9" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="9" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="9" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="9" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="9" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="9" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="9" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="9" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="9" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="9" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="9" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="9" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="9" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="9" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="9" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="9" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="9" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="9" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="9" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="9" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="9" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="9" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="9" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="9" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="9" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="9" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="9" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="9" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="9" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="9" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="9" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="9" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="9" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="9" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="9" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="9" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="9" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="9" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="9" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="B90" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="9" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="B91" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="9" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="9" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="9" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="9" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="9" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="9" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C97" s="9" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="9" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="B98" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="9" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="B99" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="9" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="B100" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="9" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="B101" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="9" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="B102" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="9" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="B103" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="9" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="9" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C105" s="9" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="9" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="9" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C107" s="9" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="9" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="B108" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C108" s="9" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="9" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C109" s="9" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="9" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="B110" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C110" s="9" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="9" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="B111" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C111" s="9" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="9" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B112" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C112" s="9" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="9" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="B113" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C113" s="9" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="9" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="B114" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C114" s="9" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="9" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="B115" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C115" s="9" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="9" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C116" s="9" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="9" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="B117" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C117" s="9" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="9" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="B118" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C118" s="9" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="9" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C119" s="9" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="9" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="B120" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C120" s="9" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="9" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="B121" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C121" s="9" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="9" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="B122" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C122" s="9" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="9" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="B123" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C123" s="9" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="9" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="B124" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C124" s="9" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="9" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="B125" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C125" s="9" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="9" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="B126" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C126" s="9" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="9" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="B127" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C127" s="9" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="9" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="B128" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C128" s="9" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="9" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="B129" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C129" s="9" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="9" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="B130" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C130" s="9" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="9" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="B131" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C131" s="9" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="9" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="B132" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C132" s="9" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="9" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="B133" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C133" s="9" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="9" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="B134" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C134" s="9" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="9" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="B135" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C135" s="9" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="9" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="B136" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C136" s="9" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="9" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="B137" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C137" s="9" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="9" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="B138" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C138" s="9" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="9" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="B139" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C139" s="9" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="9" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="B140" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C140" s="9" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="9" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="B141" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C141" s="9" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="9" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="B142" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C142" s="9" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="9" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="B143" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C143" s="9" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="9" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="B144" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C144" s="9" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="9" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="B145" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C145" s="9" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="9" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="B146" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C146" s="9" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="9" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="B147" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C147" s="9" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="9" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="B148" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C148" s="9" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="9" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="B149" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C149" s="9" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="9" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="B150" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C150" s="9" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="9" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="B151" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C151" s="9" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="9" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="B152" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C152" s="9" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="9" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="B153" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C153" s="9" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="9" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="B154" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C154" s="9" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="9" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="B155" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C155" s="9" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="9" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="B156" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C156" s="9" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="9" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="B157" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C157" s="9" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="9" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="B158" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C158" s="9" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="9" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="B159" s="9" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C159" s="9" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="9" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="B160" s="9" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="C160" s="9" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="9" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="B161" s="9" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="C161" s="9" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="9" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="B162" s="9" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="C162" s="9" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="9" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="B163" s="9" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="C163" s="9" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="9" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="B164" s="9" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="C164" s="9" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="9" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="B165" s="9" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="C165" s="9" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="9" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="B166" s="9" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="C166" s="9" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="9" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="B167" s="9" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="C167" s="9" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="9" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="B168" s="9" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="C168" s="9" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="9" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="B169" s="9" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="C169" s="9" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="9" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="B170" s="9" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="C170" s="9" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="9" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="B171" s="9" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="C171" s="9" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="9" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="B172" s="9" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="C172" s="9" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="9" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="B173" s="9" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="C173" s="9" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="9" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="B174" s="9" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="C174" s="9" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="9" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="B175" s="9" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="C175" s="9" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="9" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="B176" s="9" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="C176" s="9" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="9" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="B177" s="9" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="C177" s="9" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="9" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="B178" s="9" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="C178" s="9" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="9" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="B179" s="9" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="C179" s="9" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="9" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="B180" s="9" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="C180" s="9" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="9" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="B181" s="9" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="C181" s="9" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="9" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="B182" s="9" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="C182" s="9" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="9" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="B183" s="9" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="C183" s="9" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="9" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="B184" s="9" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="C184" s="9" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="9" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="B185" s="9" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="C185" s="9" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="9" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="B186" s="9" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="C186" s="9" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="9" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="B187" s="9" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="C187" s="9" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="9" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="B188" s="9" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="C188" s="9" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="9" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="B189" s="9" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="C189" s="9" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="9" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="B190" s="9" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="C190" s="9" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="9" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="B191" s="9" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="C191" s="9" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="9" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
       <c r="B192" s="9" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="C192" s="9" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="9" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="B193" s="9" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="C193" s="9" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="9" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="B194" s="9" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="C194" s="9" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="9" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="B195" s="9" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="C195" s="9" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="9" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="B196" s="9" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="C196" s="9" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="9" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="B197" s="9" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="C197" s="9" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="9" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="B198" s="9" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="C198" s="9" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="9" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="B199" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C199" s="9" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="9" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="B200" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C200" s="9" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="9" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
       <c r="B201" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C201" s="9" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="9" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="B202" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C202" s="9" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="9" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="B203" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C203" s="9" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="9" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="B204" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C204" s="9" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="9" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="B205" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C205" s="9" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="9" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="B206" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C206" s="9" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="9" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="B207" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C207" s="9" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="9" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
       <c r="B208" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C208" s="9" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="9" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
       <c r="B209" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C209" s="9" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="9" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="B210" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C210" s="9" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="9" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="B211" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C211" s="9" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="9" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
       <c r="B212" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C212" s="9" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="9" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="B213" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C213" s="9" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="9" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
       <c r="B214" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C214" s="9" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="9" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="B215" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C215" s="9" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="9" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="B216" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C216" s="9" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="9" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="B217" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C217" s="9" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="9" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="B218" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C218" s="9" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="9" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="B219" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C219" s="9" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="9" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="B220" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C220" s="9" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="9" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="B221" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C221" s="9" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="9" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="B222" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C222" s="9" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="9" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="B223" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C223" s="9" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="9" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
       <c r="B224" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C224" s="9" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="9" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
       <c r="B225" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C225" s="9" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="9" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
       <c r="B226" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C226" s="9" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="9" t="s">
-        <v>1098</v>
+        <v>1101</v>
       </c>
       <c r="B227" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C227" s="9" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="9" t="s">
-        <v>1100</v>
+        <v>1103</v>
       </c>
       <c r="B228" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C228" s="9" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="9" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="B229" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C229" s="9" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="9" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="B230" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C230" s="9" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="9" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="B231" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C231" s="9" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="9" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="B232" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C232" s="9" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="9" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
       <c r="B233" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C233" s="9" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="9" t="s">
-        <v>1112</v>
+        <v>1115</v>
       </c>
       <c r="B234" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C234" s="9" t="s">
-        <v>1113</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="9" t="s">
-        <v>1114</v>
+        <v>1117</v>
       </c>
       <c r="B235" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C235" s="9" t="s">
-        <v>1115</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="9" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
       <c r="B236" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C236" s="9" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="9" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
       <c r="B237" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C237" s="9" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="9" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
       <c r="B238" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C238" s="9" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="9" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="B239" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C239" s="9" t="s">
-        <v>1123</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="9" t="s">
-        <v>1124</v>
+        <v>1127</v>
       </c>
       <c r="B240" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C240" s="9" t="s">
-        <v>1125</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="9" t="s">
-        <v>1126</v>
+        <v>1129</v>
       </c>
       <c r="B241" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C241" s="9" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="9" t="s">
-        <v>1128</v>
+        <v>1131</v>
       </c>
       <c r="B242" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C242" s="9" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="9" t="s">
-        <v>1130</v>
+        <v>1133</v>
       </c>
       <c r="B243" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C243" s="9" t="s">
-        <v>1131</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="9" t="s">
-        <v>1132</v>
+        <v>1135</v>
       </c>
       <c r="B244" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C244" s="9" t="s">
-        <v>1133</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="9" t="s">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="B245" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C245" s="9" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="9" t="s">
-        <v>1136</v>
+        <v>1139</v>
       </c>
       <c r="B246" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C246" s="9" t="s">
-        <v>1137</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="9" t="s">
-        <v>1138</v>
+        <v>1141</v>
       </c>
       <c r="B247" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C247" s="9" t="s">
-        <v>1139</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="9" t="s">
-        <v>1140</v>
+        <v>1143</v>
       </c>
       <c r="B248" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C248" s="9" t="s">
-        <v>1141</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="9" t="s">
-        <v>1142</v>
+        <v>1145</v>
       </c>
       <c r="B249" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C249" s="9" t="s">
-        <v>1143</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="9" t="s">
-        <v>1144</v>
+        <v>1147</v>
       </c>
       <c r="B250" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C250" s="9" t="s">
-        <v>1145</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="9" t="s">
-        <v>1146</v>
+        <v>1149</v>
       </c>
       <c r="B251" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C251" s="9" t="s">
-        <v>1147</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="9" t="s">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="B252" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C252" s="9" t="s">
-        <v>1149</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="9" t="s">
-        <v>1150</v>
+        <v>1153</v>
       </c>
       <c r="B253" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C253" s="9" t="s">
-        <v>1151</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="9" t="s">
-        <v>1152</v>
+        <v>1155</v>
       </c>
       <c r="B254" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C254" s="9" t="s">
-        <v>1153</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="9" t="s">
-        <v>1154</v>
+        <v>1157</v>
       </c>
       <c r="B255" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C255" s="9" t="s">
-        <v>1155</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="9" t="s">
-        <v>1156</v>
+        <v>1159</v>
       </c>
       <c r="B256" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C256" s="9" t="s">
-        <v>1157</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="9" t="s">
-        <v>1158</v>
+        <v>1161</v>
       </c>
       <c r="B257" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C257" s="9" t="s">
-        <v>1159</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="9" t="s">
-        <v>1160</v>
+        <v>1163</v>
       </c>
       <c r="B258" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C258" s="9" t="s">
-        <v>1161</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="9" t="s">
-        <v>1162</v>
+        <v>1165</v>
       </c>
       <c r="B259" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C259" s="9" t="s">
-        <v>1163</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="9" t="s">
-        <v>1164</v>
+        <v>1167</v>
       </c>
       <c r="B260" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C260" s="9" t="s">
-        <v>1165</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="9" t="s">
-        <v>1166</v>
+        <v>1169</v>
       </c>
       <c r="B261" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C261" s="9" t="s">
-        <v>1167</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="9" t="s">
-        <v>1168</v>
+        <v>1171</v>
       </c>
       <c r="B262" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C262" s="9" t="s">
-        <v>1169</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="9" t="s">
-        <v>1170</v>
+        <v>1173</v>
       </c>
       <c r="B263" s="9" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C263" s="9" t="s">
-        <v>1171</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="9" t="s">
-        <v>1172</v>
+        <v>1175</v>
       </c>
       <c r="B264" s="9" t="s">
-        <v>1173</v>
+        <v>1176</v>
       </c>
       <c r="C264" s="9" t="s">
-        <v>1174</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="9" t="s">
-        <v>1175</v>
+        <v>1178</v>
       </c>
       <c r="B265" s="9" t="s">
-        <v>1173</v>
+        <v>1176</v>
       </c>
       <c r="C265" s="9" t="s">
-        <v>1176</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="9" t="s">
-        <v>1177</v>
+        <v>1180</v>
       </c>
       <c r="B266" s="9" t="s">
-        <v>1173</v>
+        <v>1176</v>
       </c>
       <c r="C266" s="9" t="s">
-        <v>1178</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="9" t="s">
-        <v>1179</v>
+        <v>1182</v>
       </c>
       <c r="B267" s="9" t="s">
-        <v>1173</v>
+        <v>1176</v>
       </c>
       <c r="C267" s="9" t="s">
-        <v>1180</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="9" t="s">
-        <v>1181</v>
+        <v>1184</v>
       </c>
       <c r="B268" s="9" t="s">
-        <v>1173</v>
+        <v>1176</v>
       </c>
       <c r="C268" s="9" t="s">
-        <v>1182</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="9" t="s">
-        <v>1183</v>
+        <v>1186</v>
       </c>
       <c r="B269" s="9" t="s">
-        <v>1173</v>
+        <v>1176</v>
       </c>
       <c r="C269" s="9" t="s">
-        <v>1184</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="9" t="s">
-        <v>1185</v>
+        <v>1188</v>
       </c>
       <c r="B270" s="9" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="C270" s="9" t="s">
-        <v>1187</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="9" t="s">
-        <v>1188</v>
+        <v>1191</v>
       </c>
       <c r="B271" s="9" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="C271" s="9" t="s">
-        <v>1189</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="9" t="s">
-        <v>1190</v>
+        <v>1193</v>
       </c>
       <c r="B272" s="9" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="C272" s="9" t="s">
-        <v>1191</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="9" t="s">
-        <v>1192</v>
+        <v>1195</v>
       </c>
       <c r="B273" s="9" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="C273" s="9" t="s">
-        <v>1193</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="9" t="s">
-        <v>1194</v>
+        <v>1197</v>
       </c>
       <c r="B274" s="9" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="C274" s="9" t="s">
-        <v>1195</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="9" t="s">
-        <v>1196</v>
+        <v>1199</v>
       </c>
       <c r="B275" s="9" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="C275" s="9" t="s">
-        <v>1197</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="9" t="s">
-        <v>1198</v>
+        <v>1201</v>
       </c>
       <c r="B276" s="9" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="C276" s="9" t="s">
-        <v>1199</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="9" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="B277" s="9" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="C277" s="9" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="9" t="s">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="B278" s="9" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="C278" s="9" t="s">
-        <v>1203</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="9" t="s">
-        <v>1204</v>
+        <v>1207</v>
       </c>
       <c r="B279" s="9" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="C279" s="9" t="s">
-        <v>1205</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="9" t="s">
-        <v>1206</v>
+        <v>1209</v>
       </c>
       <c r="B280" s="9" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="C280" s="9" t="s">
-        <v>1207</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="9" t="s">
-        <v>1208</v>
+        <v>1211</v>
       </c>
       <c r="B281" s="9" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="C281" s="9" t="s">
-        <v>1209</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="9" t="s">
-        <v>1210</v>
+        <v>1213</v>
       </c>
       <c r="B282" s="9" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="C282" s="9" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="9" t="s">
-        <v>1212</v>
+        <v>1215</v>
       </c>
       <c r="B283" s="9" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="C283" s="9" t="s">
-        <v>1213</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="9" t="s">
-        <v>1214</v>
+        <v>1217</v>
       </c>
       <c r="B284" s="9" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="C284" s="9" t="s">
-        <v>1215</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="9" t="s">
-        <v>1216</v>
+        <v>1219</v>
       </c>
       <c r="B285" s="9" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="C285" s="9" t="s">
-        <v>1217</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="9" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="B286" s="9" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="C286" s="9" t="s">
-        <v>1219</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="9" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="B287" s="9" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="C287" s="9" t="s">
-        <v>1221</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="9" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="B288" s="9" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="C288" s="9" t="s">
-        <v>1223</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="9" t="s">
-        <v>1224</v>
+        <v>1227</v>
       </c>
       <c r="B289" s="9" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="C289" s="9" t="s">
-        <v>1225</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="9" t="s">
-        <v>1226</v>
+        <v>1229</v>
       </c>
       <c r="B290" s="9" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="C290" s="9" t="s">
-        <v>1227</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="9" t="s">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="B291" s="9" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="C291" s="9" t="s">
-        <v>1229</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="9" t="s">
-        <v>1230</v>
+        <v>1233</v>
       </c>
       <c r="B292" s="9" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="C292" s="9" t="s">
-        <v>1231</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="9" t="s">
-        <v>1232</v>
+        <v>1235</v>
       </c>
       <c r="B293" s="9" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="C293" s="9" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="294" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="9" t="s">
-        <v>1234</v>
+        <v>1237</v>
       </c>
       <c r="B294" s="9" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="C294" s="9" t="s">
-        <v>1235</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="9" t="s">
-        <v>1236</v>
+        <v>1239</v>
       </c>
       <c r="B295" s="9" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="C295" s="9" t="s">
-        <v>1237</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="9" t="s">
-        <v>1238</v>
+        <v>1241</v>
       </c>
       <c r="B296" s="9" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="C296" s="9" t="s">
-        <v>1239</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="9" t="s">
-        <v>1240</v>
+        <v>1243</v>
       </c>
       <c r="B297" s="9" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="C297" s="9" t="s">
-        <v>1241</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="9" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
       <c r="B298" s="9" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="C298" s="9" t="s">
-        <v>1243</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="9" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="B299" s="9" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="C299" s="9" t="s">
-        <v>1245</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="9" t="s">
-        <v>1246</v>
+        <v>1249</v>
       </c>
       <c r="B300" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C300" s="9" t="s">
-        <v>1248</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="301" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="9" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="B301" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C301" s="9" t="s">
-        <v>1250</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="302" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="9" t="s">
-        <v>1251</v>
+        <v>1254</v>
       </c>
       <c r="B302" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C302" s="9" t="s">
-        <v>1252</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="9" t="s">
-        <v>1253</v>
+        <v>1256</v>
       </c>
       <c r="B303" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C303" s="9" t="s">
-        <v>1254</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="9" t="s">
-        <v>1255</v>
+        <v>1258</v>
       </c>
       <c r="B304" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C304" s="9" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="305" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="9" t="s">
-        <v>1257</v>
+        <v>1260</v>
       </c>
       <c r="B305" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C305" s="9" t="s">
-        <v>1258</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="9" t="s">
-        <v>1259</v>
+        <v>1262</v>
       </c>
       <c r="B306" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C306" s="9" t="s">
-        <v>1260</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="307" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A307" s="9" t="s">
-        <v>1261</v>
+        <v>1264</v>
       </c>
       <c r="B307" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C307" s="9" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="9" t="s">
-        <v>1263</v>
+        <v>1266</v>
       </c>
       <c r="B308" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C308" s="9" t="s">
-        <v>1264</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="9" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="B309" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C309" s="9" t="s">
-        <v>1266</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="9" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
       <c r="B310" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C310" s="9" t="s">
-        <v>1268</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="9" t="s">
-        <v>1269</v>
+        <v>1272</v>
       </c>
       <c r="B311" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C311" s="9" t="s">
-        <v>1270</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="312" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="9" t="s">
-        <v>1271</v>
+        <v>1274</v>
       </c>
       <c r="B312" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C312" s="9" t="s">
-        <v>1272</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="313" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="9" t="s">
-        <v>1273</v>
+        <v>1276</v>
       </c>
       <c r="B313" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C313" s="9" t="s">
-        <v>1274</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="314" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="9" t="s">
-        <v>1275</v>
+        <v>1278</v>
       </c>
       <c r="B314" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C314" s="9" t="s">
-        <v>1276</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="9" t="s">
-        <v>1277</v>
+        <v>1280</v>
       </c>
       <c r="B315" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C315" s="9" t="s">
-        <v>1278</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="9" t="s">
-        <v>1279</v>
+        <v>1282</v>
       </c>
       <c r="B316" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C316" s="9" t="s">
-        <v>1280</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="9" t="s">
-        <v>1281</v>
+        <v>1284</v>
       </c>
       <c r="B317" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C317" s="9" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="318" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="9" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="B318" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C318" s="9" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="319" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="9" t="s">
-        <v>1285</v>
+        <v>1288</v>
       </c>
       <c r="B319" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C319" s="9" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="320" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="9" t="s">
-        <v>1287</v>
+        <v>1290</v>
       </c>
       <c r="B320" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C320" s="9" t="s">
-        <v>1288</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="321" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="9" t="s">
-        <v>1289</v>
+        <v>1292</v>
       </c>
       <c r="B321" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C321" s="9" t="s">
-        <v>1290</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="322" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="9" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="B322" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C322" s="9" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="9" t="s">
-        <v>1293</v>
+        <v>1296</v>
       </c>
       <c r="B323" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C323" s="9" t="s">
-        <v>1294</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="324" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="9" t="s">
-        <v>1295</v>
+        <v>1298</v>
       </c>
       <c r="B324" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C324" s="9" t="s">
-        <v>1296</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="325" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A325" s="9" t="s">
-        <v>1297</v>
+        <v>1300</v>
       </c>
       <c r="B325" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C325" s="9" t="s">
-        <v>1298</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="326" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="9" t="s">
-        <v>1299</v>
+        <v>1302</v>
       </c>
       <c r="B326" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C326" s="9" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="327" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A327" s="9" t="s">
-        <v>1301</v>
+        <v>1304</v>
       </c>
       <c r="B327" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C327" s="9" t="s">
-        <v>1302</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="328" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A328" s="9" t="s">
-        <v>1303</v>
+        <v>1306</v>
       </c>
       <c r="B328" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C328" s="9" t="s">
-        <v>1304</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="329" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A329" s="9" t="s">
-        <v>1305</v>
+        <v>1308</v>
       </c>
       <c r="B329" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C329" s="9" t="s">
-        <v>1306</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="330" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="9" t="s">
-        <v>1307</v>
+        <v>1310</v>
       </c>
       <c r="B330" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C330" s="9" t="s">
-        <v>1308</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="9" t="s">
-        <v>1309</v>
+        <v>1312</v>
       </c>
       <c r="B331" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C331" s="9" t="s">
-        <v>1310</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="332" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="9" t="s">
-        <v>1311</v>
+        <v>1314</v>
       </c>
       <c r="B332" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C332" s="9" t="s">
-        <v>1312</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="333" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A333" s="9" t="s">
-        <v>1313</v>
+        <v>1316</v>
       </c>
       <c r="B333" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C333" s="9" t="s">
-        <v>1314</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="334" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="9" t="s">
-        <v>1315</v>
+        <v>1318</v>
       </c>
       <c r="B334" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C334" s="9" t="s">
-        <v>1316</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="335" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="9" t="s">
-        <v>1317</v>
+        <v>1320</v>
       </c>
       <c r="B335" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C335" s="9" t="s">
-        <v>1318</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="336" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="9" t="s">
-        <v>1319</v>
+        <v>1322</v>
       </c>
       <c r="B336" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C336" s="9" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="337" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="9" t="s">
-        <v>1321</v>
+        <v>1324</v>
       </c>
       <c r="B337" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C337" s="9" t="s">
-        <v>1322</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="338" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A338" s="9" t="s">
-        <v>1323</v>
+        <v>1326</v>
       </c>
       <c r="B338" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C338" s="9" t="s">
-        <v>1324</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A339" s="9" t="s">
-        <v>1325</v>
+        <v>1328</v>
       </c>
       <c r="B339" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C339" s="9" t="s">
-        <v>1326</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A340" s="9" t="s">
-        <v>1327</v>
+        <v>1330</v>
       </c>
       <c r="B340" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C340" s="9" t="s">
-        <v>1328</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A341" s="9" t="s">
-        <v>1329</v>
+        <v>1332</v>
       </c>
       <c r="B341" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C341" s="9" t="s">
-        <v>1330</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A342" s="9" t="s">
-        <v>1331</v>
+        <v>1334</v>
       </c>
       <c r="B342" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C342" s="9" t="s">
-        <v>1332</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="9" t="s">
-        <v>1333</v>
+        <v>1336</v>
       </c>
       <c r="B343" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C343" s="9" t="s">
-        <v>1334</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="344" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="9" t="s">
-        <v>1335</v>
+        <v>1338</v>
       </c>
       <c r="B344" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C344" s="9" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="345" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="9" t="s">
-        <v>1337</v>
+        <v>1340</v>
       </c>
       <c r="B345" s="9" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C345" s="9" t="s">
-        <v>1338</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="346" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A346" s="9" t="s">
-        <v>1339</v>
+        <v>1342</v>
       </c>
       <c r="B346" s="9" t="s">
-        <v>1340</v>
+        <v>1343</v>
       </c>
       <c r="C346" s="9" t="s">
-        <v>1341</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="347" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="9" t="s">
-        <v>1342</v>
+        <v>1345</v>
       </c>
       <c r="B347" s="9" t="s">
-        <v>1340</v>
+        <v>1343</v>
       </c>
       <c r="C347" s="9" t="s">
-        <v>1343</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="348" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="9" t="s">
-        <v>1344</v>
+        <v>1347</v>
       </c>
       <c r="B348" s="9" t="s">
-        <v>1340</v>
+        <v>1343</v>
       </c>
       <c r="C348" s="9" t="s">
-        <v>1345</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A349" s="9" t="s">
-        <v>1346</v>
+        <v>1349</v>
       </c>
       <c r="B349" s="9" t="s">
-        <v>1340</v>
+        <v>1343</v>
       </c>
       <c r="C349" s="9" t="s">
-        <v>1347</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="350" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="9" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
       <c r="B350" s="9" t="s">
-        <v>1340</v>
+        <v>1343</v>
       </c>
       <c r="C350" s="9" t="s">
-        <v>1349</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="9" t="s">
-        <v>1350</v>
+        <v>1353</v>
       </c>
       <c r="B351" s="9" t="s">
-        <v>1340</v>
+        <v>1343</v>
       </c>
       <c r="C351" s="9" t="s">
-        <v>1351</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="9" t="s">
-        <v>1352</v>
+        <v>1355</v>
       </c>
       <c r="B352" s="9" t="s">
-        <v>1340</v>
+        <v>1343</v>
       </c>
       <c r="C352" s="9" t="s">
-        <v>1353</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="353" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="9" t="s">
-        <v>1354</v>
+        <v>1357</v>
       </c>
       <c r="B353" s="9" t="s">
-        <v>1340</v>
+        <v>1343</v>
       </c>
       <c r="C353" s="9" t="s">
-        <v>1355</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="354" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="9" t="s">
-        <v>1356</v>
+        <v>1359</v>
       </c>
       <c r="B354" s="9" t="s">
-        <v>1340</v>
+        <v>1343</v>
       </c>
       <c r="C354" s="9" t="s">
-        <v>1357</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="9" t="s">
-        <v>1358</v>
+        <v>1361</v>
       </c>
       <c r="B355" s="9" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="C355" s="9" t="s">
-        <v>1360</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="356" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="9" t="s">
-        <v>1361</v>
+        <v>1364</v>
       </c>
       <c r="B356" s="9" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="C356" s="9" t="s">
-        <v>1362</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="357" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="9" t="s">
-        <v>1363</v>
+        <v>1366</v>
       </c>
       <c r="B357" s="9" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="C357" s="9" t="s">
-        <v>1364</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="9" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="B358" s="9" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="C358" s="9" t="s">
-        <v>1366</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="359" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="9" t="s">
-        <v>1367</v>
+        <v>1370</v>
       </c>
       <c r="B359" s="9" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="C359" s="9" t="s">
-        <v>1368</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A360" s="9" t="s">
-        <v>1369</v>
+        <v>1372</v>
       </c>
       <c r="B360" s="9" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="C360" s="9" t="s">
-        <v>1370</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A361" s="9" t="s">
-        <v>1371</v>
+        <v>1374</v>
       </c>
       <c r="B361" s="9" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="C361" s="9" t="s">
-        <v>1372</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="362" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="9" t="s">
-        <v>1373</v>
+        <v>1376</v>
       </c>
       <c r="B362" s="9" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="C362" s="9" t="s">
-        <v>1374</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="9" t="s">
-        <v>1375</v>
+        <v>1378</v>
       </c>
       <c r="B363" s="9" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="C363" s="9" t="s">
-        <v>1376</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="364" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A364" s="9" t="s">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="B364" s="9" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="C364" s="9" t="s">
-        <v>1378</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A365" s="9" t="s">
-        <v>1379</v>
+        <v>1382</v>
       </c>
       <c r="B365" s="9" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="C365" s="9" t="s">
-        <v>1380</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="366" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="9" t="s">
-        <v>1381</v>
+        <v>1384</v>
       </c>
       <c r="B366" s="9" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="C366" s="9" t="s">
-        <v>1382</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="367" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="9" t="s">
-        <v>1383</v>
+        <v>1386</v>
       </c>
       <c r="B367" s="9" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="C367" s="9" t="s">
-        <v>1384</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="368" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A368" s="9" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="B368" s="9" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="C368" s="9" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="369" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A369" s="9" t="s">
-        <v>1387</v>
+        <v>1390</v>
       </c>
       <c r="B369" s="9" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="C369" s="9" t="s">
-        <v>1388</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="370" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A370" s="9" t="s">
-        <v>1389</v>
+        <v>1392</v>
       </c>
       <c r="B370" s="9" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="C370" s="9" t="s">
-        <v>1390</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="371" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A371" s="9" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="B371" s="9" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="C371" s="9" t="s">
-        <v>1392</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="372" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="9" t="s">
-        <v>1393</v>
+        <v>1396</v>
       </c>
       <c r="B372" s="9" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="C372" s="9" t="s">
-        <v>1394</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="373" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="9" t="s">
-        <v>1395</v>
+        <v>1398</v>
       </c>
       <c r="B373" s="9" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="C373" s="9" t="s">
-        <v>1396</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="374" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A374" s="9" t="s">
-        <v>1397</v>
+        <v>1400</v>
       </c>
       <c r="B374" s="9" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="C374" s="9" t="s">
-        <v>1398</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="375" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A375" s="9" t="s">
-        <v>1399</v>
+        <v>1402</v>
       </c>
       <c r="B375" s="9" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="C375" s="9" t="s">
-        <v>1400</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="376" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="9" t="s">
-        <v>1401</v>
+        <v>1404</v>
       </c>
       <c r="B376" s="9" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="C376" s="9" t="s">
-        <v>1402</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="377" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A377" s="9" t="s">
-        <v>1403</v>
+        <v>1406</v>
       </c>
       <c r="B377" s="9" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="C377" s="9" t="s">
-        <v>1404</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="378" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="9" t="s">
-        <v>1405</v>
+        <v>1408</v>
       </c>
       <c r="B378" s="9" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="C378" s="9" t="s">
-        <v>1406</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="379" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="9" t="s">
-        <v>1407</v>
+        <v>1410</v>
       </c>
       <c r="B379" s="9" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="C379" s="9" t="s">
-        <v>1408</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="380" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="9" t="s">
-        <v>1409</v>
+        <v>1412</v>
       </c>
       <c r="B380" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C380" s="9" t="s">
-        <v>1411</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="381" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A381" s="9" t="s">
-        <v>1412</v>
+        <v>1415</v>
       </c>
       <c r="B381" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C381" s="9" t="s">
-        <v>1413</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="382" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A382" s="9" t="s">
-        <v>1414</v>
+        <v>1417</v>
       </c>
       <c r="B382" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C382" s="9" t="s">
-        <v>1415</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="383" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A383" s="9" t="s">
-        <v>1416</v>
+        <v>1419</v>
       </c>
       <c r="B383" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C383" s="9" t="s">
-        <v>1417</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="384" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A384" s="9" t="s">
-        <v>1418</v>
+        <v>1421</v>
       </c>
       <c r="B384" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C384" s="9" t="s">
-        <v>1419</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="385" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A385" s="9" t="s">
-        <v>1420</v>
+        <v>1423</v>
       </c>
       <c r="B385" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C385" s="9" t="s">
-        <v>1421</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="386" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A386" s="9" t="s">
-        <v>1422</v>
+        <v>1425</v>
       </c>
       <c r="B386" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C386" s="9" t="s">
-        <v>1423</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="387" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A387" s="9" t="s">
-        <v>1424</v>
+        <v>1427</v>
       </c>
       <c r="B387" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C387" s="9" t="s">
-        <v>1425</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="388" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A388" s="9" t="s">
-        <v>1426</v>
+        <v>1429</v>
       </c>
       <c r="B388" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C388" s="9" t="s">
-        <v>1427</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="389" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A389" s="9" t="s">
-        <v>1428</v>
+        <v>1431</v>
       </c>
       <c r="B389" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C389" s="9" t="s">
-        <v>1429</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="390" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A390" s="9" t="s">
-        <v>1430</v>
+        <v>1433</v>
       </c>
       <c r="B390" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C390" s="9" t="s">
-        <v>1431</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="391" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A391" s="9" t="s">
-        <v>1432</v>
+        <v>1435</v>
       </c>
       <c r="B391" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C391" s="9" t="s">
-        <v>1433</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="392" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A392" s="9" t="s">
-        <v>1434</v>
+        <v>1437</v>
       </c>
       <c r="B392" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C392" s="9" t="s">
-        <v>1435</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="393" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A393" s="9" t="s">
-        <v>1436</v>
+        <v>1439</v>
       </c>
       <c r="B393" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C393" s="9" t="s">
-        <v>1437</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="394" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A394" s="9" t="s">
-        <v>1438</v>
+        <v>1441</v>
       </c>
       <c r="B394" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C394" s="9" t="s">
-        <v>1439</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="395" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A395" s="9" t="s">
-        <v>1440</v>
+        <v>1443</v>
       </c>
       <c r="B395" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C395" s="9" t="s">
-        <v>1441</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="396" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A396" s="9" t="s">
-        <v>1442</v>
+        <v>1445</v>
       </c>
       <c r="B396" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C396" s="9" t="s">
-        <v>1443</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="397" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A397" s="9" t="s">
-        <v>1444</v>
+        <v>1447</v>
       </c>
       <c r="B397" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C397" s="9" t="s">
-        <v>1445</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="398" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A398" s="9" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="B398" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C398" s="9" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="399" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A399" s="9" t="s">
-        <v>1448</v>
+        <v>1451</v>
       </c>
       <c r="B399" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C399" s="9" t="s">
-        <v>1449</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="400" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="9" t="s">
-        <v>1450</v>
+        <v>1453</v>
       </c>
       <c r="B400" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C400" s="9" t="s">
-        <v>1451</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="401" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="9" t="s">
-        <v>1452</v>
+        <v>1455</v>
       </c>
       <c r="B401" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C401" s="9" t="s">
-        <v>1453</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="402" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="9" t="s">
-        <v>1454</v>
+        <v>1457</v>
       </c>
       <c r="B402" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C402" s="9" t="s">
-        <v>1455</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="403" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A403" s="9" t="s">
-        <v>1456</v>
+        <v>1459</v>
       </c>
       <c r="B403" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C403" s="9" t="s">
-        <v>1457</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="404" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A404" s="9" t="s">
-        <v>1458</v>
+        <v>1461</v>
       </c>
       <c r="B404" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C404" s="9" t="s">
-        <v>1459</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="405" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A405" s="9" t="s">
-        <v>1460</v>
+        <v>1463</v>
       </c>
       <c r="B405" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C405" s="9" t="s">
-        <v>1461</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="406" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A406" s="9" t="s">
-        <v>1462</v>
+        <v>1465</v>
       </c>
       <c r="B406" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C406" s="9" t="s">
-        <v>1463</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="407" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A407" s="9" t="s">
-        <v>1464</v>
+        <v>1467</v>
       </c>
       <c r="B407" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C407" s="9" t="s">
-        <v>1465</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="408" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A408" s="9" t="s">
-        <v>1466</v>
+        <v>1469</v>
       </c>
       <c r="B408" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C408" s="9" t="s">
-        <v>1467</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="409" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A409" s="9" t="s">
-        <v>1468</v>
+        <v>1471</v>
       </c>
       <c r="B409" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C409" s="9" t="s">
-        <v>1469</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="410" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A410" s="9" t="s">
-        <v>1470</v>
+        <v>1473</v>
       </c>
       <c r="B410" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C410" s="9" t="s">
-        <v>1471</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="411" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="9" t="s">
-        <v>1472</v>
+        <v>1475</v>
       </c>
       <c r="B411" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C411" s="9" t="s">
-        <v>1473</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="412" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A412" s="9" t="s">
-        <v>1474</v>
+        <v>1477</v>
       </c>
       <c r="B412" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C412" s="9" t="s">
-        <v>1475</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="413" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A413" s="9" t="s">
-        <v>1476</v>
+        <v>1479</v>
       </c>
       <c r="B413" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C413" s="9" t="s">
-        <v>1477</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="414" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A414" s="9" t="s">
-        <v>1478</v>
+        <v>1481</v>
       </c>
       <c r="B414" s="9" t="s">
-        <v>1479</v>
+        <v>1482</v>
       </c>
       <c r="C414" s="9" t="s">
-        <v>1480</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="415" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A415" s="9" t="s">
-        <v>1481</v>
+        <v>1484</v>
       </c>
       <c r="B415" s="9" t="s">
-        <v>1479</v>
+        <v>1482</v>
       </c>
       <c r="C415" s="9" t="s">
-        <v>1482</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="416" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A416" s="9" t="s">
-        <v>1483</v>
+        <v>1486</v>
       </c>
       <c r="B416" s="9" t="s">
-        <v>1479</v>
+        <v>1482</v>
       </c>
       <c r="C416" s="9" t="s">
-        <v>1484</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="417" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A417" s="9" t="s">
-        <v>1485</v>
+        <v>1488</v>
       </c>
       <c r="B417" s="9" t="s">
-        <v>1479</v>
+        <v>1482</v>
       </c>
       <c r="C417" s="9" t="s">
-        <v>1486</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="418" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A418" s="9" t="s">
-        <v>1487</v>
+        <v>1490</v>
       </c>
       <c r="B418" s="9" t="s">
-        <v>1479</v>
+        <v>1482</v>
       </c>
       <c r="C418" s="9" t="s">
-        <v>1488</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="419" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A419" s="9" t="s">
-        <v>1489</v>
+        <v>1492</v>
       </c>
       <c r="B419" s="9" t="s">
-        <v>1479</v>
+        <v>1482</v>
       </c>
       <c r="C419" s="9" t="s">
-        <v>1490</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="420" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A420" s="9" t="s">
-        <v>1491</v>
+        <v>1494</v>
       </c>
       <c r="B420" s="9" t="s">
-        <v>1479</v>
+        <v>1482</v>
       </c>
       <c r="C420" s="9" t="s">
-        <v>1492</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="421" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A421" s="9" t="s">
-        <v>1493</v>
+        <v>1496</v>
       </c>
       <c r="B421" s="9" t="s">
-        <v>1479</v>
+        <v>1482</v>
       </c>
       <c r="C421" s="9" t="s">
-        <v>1494</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="422" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A422" s="9" t="s">
-        <v>1495</v>
+        <v>1498</v>
       </c>
       <c r="B422" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C422" s="9" t="s">
-        <v>1496</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="423" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="9" t="s">
-        <v>1497</v>
+        <v>1500</v>
       </c>
       <c r="B423" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C423" s="9" t="s">
-        <v>1498</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="424" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A424" s="9" t="s">
-        <v>1499</v>
+        <v>1502</v>
       </c>
       <c r="B424" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C424" s="9" t="s">
-        <v>1500</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="425" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A425" s="9" t="s">
-        <v>1501</v>
+        <v>1504</v>
       </c>
       <c r="B425" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C425" s="9" t="s">
-        <v>1502</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="426" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A426" s="9" t="s">
-        <v>1503</v>
+        <v>1506</v>
       </c>
       <c r="B426" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C426" s="9" t="s">
-        <v>1504</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="427" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A427" s="9" t="s">
-        <v>1505</v>
+        <v>1508</v>
       </c>
       <c r="B427" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C427" s="9" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="428" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A428" s="9" t="s">
-        <v>1507</v>
+        <v>1510</v>
       </c>
       <c r="B428" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C428" s="9" t="s">
-        <v>1508</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="429" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="9" t="s">
-        <v>1509</v>
+        <v>1512</v>
       </c>
       <c r="B429" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C429" s="9" t="s">
-        <v>1510</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="430" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="9" t="s">
-        <v>1511</v>
+        <v>1514</v>
       </c>
       <c r="B430" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C430" s="9" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="431" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A431" s="9" t="s">
-        <v>1513</v>
+        <v>1516</v>
       </c>
       <c r="B431" s="9" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C431" s="9" t="s">
-        <v>1514</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
